--- a/packages/calculators/src/modules/test/4.7-other-livestock-manure/4.7-other-livestock-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.7-other-livestock-manure/4.7-other-livestock-manure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/4.7-other-livestock-manure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/4.7-other-livestock-manure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E86353-5B81-F642-99C6-87961E66214A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD764D7-C81C-164A-910C-77EE6504A08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14540" yWindow="2720" windowWidth="28800" windowHeight="25760" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="4.7.1.1" sheetId="1" r:id="rId1"/>
@@ -1300,7 +1300,7 @@
         <v>2.73</v>
       </c>
       <c r="K11">
-        <f t="shared" ref="K11:K30" si="0">$AQ$5</f>
+        <f>$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L11" t="s">
@@ -1311,11 +1311,11 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <f>IF(L11="yes", 1, 0.95)</f>
+        <f>IF(L11="yes", 1, 0.9966)</f>
         <v>1</v>
       </c>
       <c r="O11">
-        <f t="shared" ref="O11:O30" si="1">$AN$4</f>
+        <f t="shared" ref="O11:O29" si="0">$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P11">
@@ -1335,15 +1335,15 @@
         <v>0.21</v>
       </c>
       <c r="T11">
-        <f t="shared" ref="T11:T30" si="2">$AQ$3</f>
+        <f t="shared" ref="T11:T29" si="1">$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U11">
-        <f t="shared" ref="U11:U30" si="3">$AQ$4</f>
+        <f t="shared" ref="U11:U29" si="2">$AQ$4</f>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V11">
-        <f t="shared" ref="V11:V30" si="4">$AN$5</f>
+        <f t="shared" ref="V11:V29" si="3">$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="W11">
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <f t="shared" ref="Z11:Z30" si="5">$AM$33</f>
+        <f t="shared" ref="Z11:Z29" si="4">$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA11">
@@ -1440,7 +1440,7 @@
         <v>95</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" ref="H12:H30" si="6">VLOOKUP(G12,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" ref="H12:H17" si="5">VLOOKUP(G12,$AR$31:$AS$40,2,FALSE)</f>
         <v>wet</v>
       </c>
       <c r="I12" t="s">
@@ -1451,7 +1451,7 @@
         <v>2.73</v>
       </c>
       <c r="K12">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K12:K29" si="6">$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L12" t="s">
@@ -1462,11 +1462,11 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IF(L12="yes", 1, 0.95)</f>
+        <f>IF(L12="yes", 1, 0.9966)</f>
         <v>1</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P12">
@@ -1482,23 +1482,23 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S12:S30" si="7">$AN$3</f>
+        <f t="shared" ref="S12:S29" si="7">$AN$3</f>
         <v>0.21</v>
       </c>
       <c r="T12">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U12">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U12">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V12">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W12">
-        <f t="shared" ref="W12:W30" si="8">IF(H12="wet",$AN$6,$AN$7)</f>
+        <f t="shared" ref="W12:W17" si="8">IF(H12="wet",$AN$6,$AN$7)</f>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X12">
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA12">
@@ -1530,27 +1530,27 @@
         <v>3.6219634214400007E-3</v>
       </c>
       <c r="AE12">
-        <f t="shared" ref="AE12:AE30" si="9">C12*P12*365</f>
+        <f t="shared" ref="AE12:AE17" si="9">C12*P12*365</f>
         <v>86505</v>
       </c>
       <c r="AF12">
-        <f t="shared" ref="AF12:AF30" si="10">AE12*W12*O12*10^-3</f>
+        <f t="shared" ref="AF12:AF17" si="10">AE12*W12*O12*10^-3</f>
         <v>0.81561857142857142</v>
       </c>
       <c r="AG12">
-        <f t="shared" ref="AG12:AG30" si="11">AE12*S12</f>
+        <f t="shared" ref="AG12:AG17" si="11">AE12*S12</f>
         <v>18166.05</v>
       </c>
       <c r="AH12">
-        <f t="shared" ref="AH12:AH30" si="12">AG12*Q12*O12*10^-3</f>
+        <f t="shared" ref="AH12:AH17" si="12">AG12*Q12*O12*10^-3</f>
         <v>0.19982654999999999</v>
       </c>
       <c r="AI12">
-        <f t="shared" ref="AI12:AI30" si="13">AE12*R12*T12</f>
+        <f t="shared" ref="AI12:AI17" si="13">AE12*R12*T12</f>
         <v>0</v>
       </c>
       <c r="AJ12">
-        <f t="shared" ref="AJ12:AJ30" si="14">AI12*U12*O12*10^-3</f>
+        <f t="shared" ref="AJ12:AJ17" si="14">AI12*U12*O12*10^-3</f>
         <v>0</v>
       </c>
       <c r="AM12" s="2" t="s">
@@ -1591,45 +1591,45 @@
         <v>96</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>wet</v>
       </c>
       <c r="I13" t="s">
         <v>65</v>
       </c>
       <c r="J13">
-        <f t="shared" ref="J13:J30" si="15">VLOOKUP(A13, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" ref="J13:J17" si="15">VLOOKUP(A13, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L13" t="s">
         <v>55</v>
       </c>
       <c r="M13">
-        <f t="shared" ref="M13:M30" si="16">1-N13</f>
+        <f t="shared" ref="M13:M17" si="16">1-N13</f>
         <v>0</v>
       </c>
       <c r="N13">
-        <f t="shared" ref="N13:N30" si="17">IF(L13="yes", 1, 0.95)</f>
+        <f t="shared" ref="N13:N29" si="17">IF(L13="yes", 1, 0.9966)</f>
         <v>1</v>
       </c>
       <c r="O13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P13">
-        <f t="shared" ref="P13:P30" si="18">VLOOKUP(A13, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" ref="P13:P17" si="18">VLOOKUP(A13, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q13">
-        <f t="shared" ref="Q13:Q30" si="19">VLOOKUP(E13,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" ref="Q13:Q17" si="19">VLOOKUP(E13,$AR$10:$AS$22,2,FALSE)</f>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R13:R30" si="20">IF(D13="yes", 1, 0)</f>
+        <f t="shared" ref="R13:R17" si="20">IF(D13="yes", 1, 0)</f>
         <v>1</v>
       </c>
       <c r="S13">
@@ -1637,15 +1637,15 @@
         <v>0.21</v>
       </c>
       <c r="T13">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U13">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U13">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V13">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W13">
@@ -1653,31 +1653,31 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="X13">
-        <f t="shared" ref="X13:X30" si="21">VLOOKUP(I13,$AM$23:$AN$30,2,FALSE)</f>
+        <f t="shared" ref="X13:X17" si="21">VLOOKUP(I13,$AM$23:$AN$30,2,FALSE)</f>
         <v>0.78</v>
       </c>
       <c r="Y13">
-        <f t="shared" ref="Y13:Y30" si="22">J13*K13*M13*X13*V13</f>
+        <f t="shared" ref="Y13:Y17" si="22">J13*K13*M13*X13*V13</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA13">
-        <f t="shared" ref="AA13:AA30" si="23">J13*K13*N13*Z13*V13</f>
+        <f t="shared" ref="AA13:AA17" si="23">J13*K13*N13*Z13*V13</f>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB13">
-        <f t="shared" ref="AB13:AB30" si="24">C13*Y13*365</f>
+        <f t="shared" ref="AB13:AB17" si="24">C13*Y13*365</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f t="shared" ref="AC13:AC30" si="25">C13*AA13*365</f>
+        <f t="shared" ref="AC13:AC17" si="25">C13*AA13*365</f>
         <v>4.22562399168</v>
       </c>
       <c r="AD13">
-        <f t="shared" ref="AD13:AD30" si="26">(AB13+AC13)*10^-3</f>
+        <f t="shared" ref="AD13:AD17" si="26">(AB13+AC13)*10^-3</f>
         <v>4.2256239916799998E-3</v>
       </c>
       <c r="AE13">
@@ -1742,7 +1742,7 @@
         <v>97</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>wet</v>
       </c>
       <c r="I14" t="s">
@@ -1753,7 +1753,7 @@
         <v>2.73</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L14" t="s">
@@ -1768,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="O14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P14">
@@ -1788,15 +1788,15 @@
         <v>0.21</v>
       </c>
       <c r="T14">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U14">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U14">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V14">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W14">
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA14">
@@ -1893,7 +1893,7 @@
         <v>98</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>wet</v>
       </c>
       <c r="I15" t="s">
@@ -1904,7 +1904,7 @@
         <v>0.34</v>
       </c>
       <c r="K15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L15" t="s">
@@ -1919,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="O15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P15">
@@ -1939,15 +1939,15 @@
         <v>0.21</v>
       </c>
       <c r="T15">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U15">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U15">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V15">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W15">
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA15">
@@ -2044,7 +2044,7 @@
         <v>99</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>wet</v>
       </c>
       <c r="I16" s="2" t="s">
@@ -2055,7 +2055,7 @@
         <v>0.34</v>
       </c>
       <c r="K16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L16" t="s">
@@ -2070,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="O16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P16">
@@ -2090,15 +2090,15 @@
         <v>0.21</v>
       </c>
       <c r="T16">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U16">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U16">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V16">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V16">
-        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W16">
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA16">
@@ -2195,7 +2195,7 @@
         <v>100</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>dry</v>
       </c>
       <c r="I17" s="2" t="s">
@@ -2206,7 +2206,7 @@
         <v>0.34</v>
       </c>
       <c r="K17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L17" t="s">
@@ -2221,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="O17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P17">
@@ -2241,15 +2241,15 @@
         <v>0.21</v>
       </c>
       <c r="T17">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U17">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U17">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V17">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="4"/>
         <v>0.6784</v>
       </c>
       <c r="W17">
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA17">
@@ -2346,45 +2346,45 @@
         <v>102</v>
       </c>
       <c r="H18" t="str">
-        <f>VLOOKUP(G18,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" ref="H18:H29" si="27">VLOOKUP(G18,$AR$31:$AS$40,2,FALSE)</f>
         <v>dry</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J18">
-        <f>VLOOKUP(A18, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" ref="J18:J29" si="28">VLOOKUP(A18, $AM$11:$AN$18,2,FALSE)</f>
         <v>0.34</v>
       </c>
       <c r="K18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L18" t="s">
         <v>55</v>
       </c>
       <c r="M18">
-        <f>1-N18</f>
+        <f t="shared" ref="M18:M29" si="29">1-N18</f>
         <v>0</v>
       </c>
       <c r="N18">
-        <f>IF(L18="yes", 1, 0.95)</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P18">
-        <f>VLOOKUP(A18, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" ref="P18:P29" si="30">VLOOKUP(A18, $AM$11:$AO$18,3,FALSE)</f>
         <v>7</v>
       </c>
       <c r="Q18">
-        <f>VLOOKUP(E18,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" ref="Q18:Q29" si="31">VLOOKUP(E18,$AR$10:$AS$22,2,FALSE)</f>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R18">
-        <f>IF(D18="yes", 1, 0)</f>
+        <f t="shared" ref="R18:R29" si="32">IF(D18="yes", 1, 0)</f>
         <v>1</v>
       </c>
       <c r="S18">
@@ -2392,71 +2392,71 @@
         <v>0.21</v>
       </c>
       <c r="T18">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U18">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U18">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V18">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V18">
+        <v>0.6784</v>
+      </c>
+      <c r="W18">
+        <f t="shared" ref="W18:W29" si="33">IF(H18="wet",$AN$6,$AN$7)</f>
+        <v>2E-3</v>
+      </c>
+      <c r="X18">
+        <f t="shared" ref="X18:X29" si="34">VLOOKUP(I18,$AM$23:$AN$30,2,FALSE)</f>
+        <v>0.78</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" ref="Y18:Y29" si="35">J18*K18*M18*X18*V18</f>
+        <v>0</v>
+      </c>
+      <c r="Z18">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W18">
-        <f>IF(H18="wet",$AN$6,$AN$7)</f>
-        <v>2E-3</v>
-      </c>
-      <c r="X18">
-        <f>VLOOKUP(I18,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.78</v>
-      </c>
-      <c r="Y18">
-        <f>J18*K18*M18*X18*V18</f>
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA18">
-        <f>J18*K18*N18*Z18*V18</f>
+        <f t="shared" ref="AA18:AA29" si="36">J18*K18*N18*Z18*V18</f>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB18">
-        <f>C18*Y18*365</f>
+        <f t="shared" ref="AB18:AB29" si="37">C18*Y18*365</f>
         <v>0</v>
       </c>
       <c r="AC18">
-        <f>C18*AA18*365</f>
+        <f t="shared" ref="AC18:AC29" si="38">C18*AA18*365</f>
         <v>0.97735520896000017</v>
       </c>
       <c r="AD18">
-        <f>(AB18+AC18)*10^-3</f>
+        <f t="shared" ref="AD18:AD29" si="39">(AB18+AC18)*10^-3</f>
         <v>9.7735520896000019E-4</v>
       </c>
       <c r="AE18">
-        <f>C18*P18*365</f>
+        <f t="shared" ref="AE18:AE29" si="40">C18*P18*365</f>
         <v>33215</v>
       </c>
       <c r="AF18">
-        <f>AE18*W18*O18*10^-3</f>
+        <f t="shared" ref="AF18:AF29" si="41">AE18*W18*O18*10^-3</f>
         <v>0.10439000000000001</v>
       </c>
       <c r="AG18">
-        <f>AE18*S18</f>
+        <f t="shared" ref="AG18:AG29" si="42">AE18*S18</f>
         <v>6975.15</v>
       </c>
       <c r="AH18">
-        <f>AG18*Q18*O18*10^-3</f>
+        <f t="shared" ref="AH18:AH29" si="43">AG18*Q18*O18*10^-3</f>
         <v>7.6726649999999993E-2</v>
       </c>
       <c r="AI18">
-        <f>AE18*R18*T18</f>
+        <f t="shared" ref="AI18:AI29" si="44">AE18*R18*T18</f>
         <v>7971.5999999999995</v>
       </c>
       <c r="AJ18">
-        <f>AI18*U18*O18*10^-3</f>
+        <f t="shared" ref="AJ18:AJ29" si="45">AI18*U18*O18*10^-3</f>
         <v>0.1377948</v>
       </c>
       <c r="AM18" s="2" t="s">
@@ -2497,45 +2497,45 @@
         <v>103</v>
       </c>
       <c r="H19" t="str">
-        <f>VLOOKUP(G19,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>dry</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>66</v>
       </c>
       <c r="J19">
-        <f>VLOOKUP(A19, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>0.34</v>
       </c>
       <c r="K19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L19" t="s">
         <v>55</v>
       </c>
       <c r="M19">
-        <f>1-N19</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N19">
-        <f>IF(L19="yes", 1, 0.95)</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P19">
-        <f>VLOOKUP(A19, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>7</v>
       </c>
       <c r="Q19">
-        <f>VLOOKUP(E19,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>1.8E-3</v>
       </c>
       <c r="R19">
-        <f>IF(D19="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="S19">
@@ -2543,71 +2543,71 @@
         <v>0.21</v>
       </c>
       <c r="T19">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U19">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U19">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V19">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V19">
+        <v>0.6784</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="33"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="34"/>
+        <v>0.74</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z19">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W19">
-        <f>IF(H19="wet",$AN$6,$AN$7)</f>
-        <v>2E-3</v>
-      </c>
-      <c r="X19">
-        <f>VLOOKUP(I19,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.74</v>
-      </c>
-      <c r="Y19">
-        <f>J19*K19*M19*X19*V19</f>
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA19">
-        <f>J19*K19*N19*Z19*V19</f>
+        <f t="shared" si="36"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB19">
-        <f>C19*Y19*365</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AC19">
-        <f>C19*AA19*365</f>
+        <f t="shared" si="38"/>
         <v>1.0525363788800002</v>
       </c>
       <c r="AD19">
-        <f>(AB19+AC19)*10^-3</f>
+        <f t="shared" si="39"/>
         <v>1.0525363788800003E-3</v>
       </c>
       <c r="AE19">
-        <f>C19*P19*365</f>
+        <f t="shared" si="40"/>
         <v>35770</v>
       </c>
       <c r="AF19">
-        <f>AE19*W19*O19*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.11242000000000001</v>
       </c>
       <c r="AG19">
-        <f>AE19*S19</f>
+        <f t="shared" si="42"/>
         <v>7511.7</v>
       </c>
       <c r="AH19">
-        <f>AG19*Q19*O19*10^-3</f>
+        <f t="shared" si="43"/>
         <v>2.1247379999999996E-2</v>
       </c>
       <c r="AI19">
-        <f>AE19*R19*T19</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="AJ19">
-        <f>AI19*U19*O19*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AP19" s="2"/>
@@ -2639,45 +2639,45 @@
         <v>94</v>
       </c>
       <c r="H20" t="str">
-        <f>VLOOKUP(G20,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>wet</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J20">
-        <f>VLOOKUP(A20, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>0.34</v>
       </c>
       <c r="K20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L20" t="s">
         <v>55</v>
       </c>
       <c r="M20">
-        <f>1-N20</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N20">
-        <f>IF(L20="yes", 1, 0.95)</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P20">
-        <f>VLOOKUP(A20, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>7</v>
       </c>
       <c r="Q20">
-        <f>VLOOKUP(E20,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="R20">
-        <f>IF(D20="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="S20">
@@ -2685,71 +2685,71 @@
         <v>0.21</v>
       </c>
       <c r="T20">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U20">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U20">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V20">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V20">
+        <v>0.6784</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="33"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="34"/>
+        <v>0.7</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z20">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W20">
-        <f>IF(H20="wet",$AN$6,$AN$7)</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X20">
-        <f>VLOOKUP(I20,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.7</v>
-      </c>
-      <c r="Y20">
-        <f>J20*K20*M20*X20*V20</f>
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA20">
-        <f>J20*K20*N20*Z20*V20</f>
+        <f t="shared" si="36"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB20">
-        <f>C20*Y20*365</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AC20">
-        <f>C20*AA20*365</f>
+        <f t="shared" si="38"/>
         <v>1.1277175488000002</v>
       </c>
       <c r="AD20">
-        <f>(AB20+AC20)*10^-3</f>
+        <f t="shared" si="39"/>
         <v>1.1277175488000003E-3</v>
       </c>
       <c r="AE20">
-        <f>C20*P20*365</f>
+        <f t="shared" si="40"/>
         <v>38325</v>
       </c>
       <c r="AF20">
-        <f>AE20*W20*O20*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.36135</v>
       </c>
       <c r="AG20">
-        <f>AE20*S20</f>
+        <f t="shared" si="42"/>
         <v>8048.25</v>
       </c>
       <c r="AH20">
-        <f>AG20*Q20*O20*10^-3</f>
+        <f t="shared" si="43"/>
         <v>3.6677024999999995E-2</v>
       </c>
       <c r="AI20">
-        <f>AE20*R20*T20</f>
+        <f t="shared" si="44"/>
         <v>9198</v>
       </c>
       <c r="AJ20">
-        <f>AI20*U20*O20*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0.158994</v>
       </c>
       <c r="AP20" s="2"/>
@@ -2781,45 +2781,45 @@
         <v>95</v>
       </c>
       <c r="H21" t="str">
-        <f>VLOOKUP(G21,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>wet</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>68</v>
       </c>
       <c r="J21">
-        <f>VLOOKUP(A21, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>0.91</v>
       </c>
       <c r="K21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L21" t="s">
         <v>55</v>
       </c>
       <c r="M21">
-        <f>1-N21</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N21">
-        <f>IF(L21="yes", 1, 0.95)</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P21">
-        <f>VLOOKUP(A21, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>13.2</v>
       </c>
       <c r="Q21">
-        <f>VLOOKUP(E21,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="R21">
-        <f>IF(D21="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="S21">
@@ -2827,71 +2827,71 @@
         <v>0.21</v>
       </c>
       <c r="T21">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U21">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U21">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V21">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V21">
+        <v>0.6784</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="33"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X21">
+        <f t="shared" si="34"/>
+        <v>0.74</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z21">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W21">
-        <f>IF(H21="wet",$AN$6,$AN$7)</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X21">
-        <f>VLOOKUP(I21,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.74</v>
-      </c>
-      <c r="Y21">
-        <f>J21*K21*M21*X21*V21</f>
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA21">
-        <f>J21*K21*N21*Z21*V21</f>
+        <f t="shared" si="36"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB21">
-        <f>C21*Y21*365</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AC21">
-        <f>C21*AA21*365</f>
+        <f t="shared" si="38"/>
         <v>3.21952304128</v>
       </c>
       <c r="AD21">
-        <f>(AB21+AC21)*10^-3</f>
+        <f t="shared" si="39"/>
         <v>3.21952304128E-3</v>
       </c>
       <c r="AE21">
-        <f>C21*P21*365</f>
+        <f t="shared" si="40"/>
         <v>77088</v>
       </c>
       <c r="AF21">
-        <f>AE21*W21*O21*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.7268297142857143</v>
       </c>
       <c r="AG21">
-        <f>AE21*S21</f>
+        <f t="shared" si="42"/>
         <v>16188.48</v>
       </c>
       <c r="AH21">
-        <f>AG21*Q21*O21*10^-3</f>
+        <f t="shared" si="43"/>
         <v>0.20351232</v>
       </c>
       <c r="AI21">
-        <f>AE21*R21*T21</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="AJ21">
-        <f>AI21*U21*O21*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AM21" s="2" t="s">
@@ -2929,45 +2929,45 @@
         <v>96</v>
       </c>
       <c r="H22" t="str">
-        <f>VLOOKUP(G22,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>wet</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="J22">
-        <f>VLOOKUP(A22, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>0.91</v>
       </c>
       <c r="K22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L22" t="s">
         <v>55</v>
       </c>
       <c r="M22">
-        <f>1-N22</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="N22">
-        <f>IF(L22="yes", 1, 0.95)</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P22">
-        <f>VLOOKUP(A22, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>13.2</v>
       </c>
       <c r="Q22">
-        <f>VLOOKUP(E22,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R22">
-        <f>IF(D22="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="S22">
@@ -2975,71 +2975,71 @@
         <v>0.21</v>
       </c>
       <c r="T22">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U22">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U22">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V22">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V22">
+        <v>0.6784</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="33"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X22">
+        <f t="shared" si="34"/>
+        <v>0.76</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Z22">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W22">
-        <f>IF(H22="wet",$AN$6,$AN$7)</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X22">
-        <f>VLOOKUP(I22,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.76</v>
-      </c>
-      <c r="Y22">
-        <f>J22*K22*M22*X22*V22</f>
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA22">
-        <f>J22*K22*N22*Z22*V22</f>
+        <f t="shared" si="36"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB22">
-        <f>C22*Y22*365</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AC22">
-        <f>C22*AA22*365</f>
+        <f t="shared" si="38"/>
         <v>3.4207432313599999</v>
       </c>
       <c r="AD22">
-        <f>(AB22+AC22)*10^-3</f>
+        <f t="shared" si="39"/>
         <v>3.4207432313600001E-3</v>
       </c>
       <c r="AE22">
-        <f>C22*P22*365</f>
+        <f t="shared" si="40"/>
         <v>81905.999999999985</v>
       </c>
       <c r="AF22">
-        <f>AE22*W22*O22*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.77225657142857129</v>
       </c>
       <c r="AG22">
-        <f>AE22*S22</f>
+        <f t="shared" si="42"/>
         <v>17200.259999999995</v>
       </c>
       <c r="AH22">
-        <f>AG22*Q22*O22*10^-3</f>
+        <f t="shared" si="43"/>
         <v>0.15947098199999993</v>
       </c>
       <c r="AI22">
-        <f>AE22*R22*T22</f>
+        <f t="shared" si="44"/>
         <v>19657.439999999995</v>
       </c>
       <c r="AJ22">
-        <f>AI22*U22*O22*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0.33979289142857128</v>
       </c>
       <c r="AM22" s="2" t="s">
@@ -3072,45 +3072,45 @@
         <v>97</v>
       </c>
       <c r="H23" t="str">
-        <f>VLOOKUP(G23,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>wet</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="J23">
-        <f>VLOOKUP(A23, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>0.91</v>
       </c>
       <c r="K23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L23" t="s">
         <v>56</v>
       </c>
       <c r="M23">
-        <f>1-N23</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="29"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N23">
-        <f>IF(L23="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="17"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P23">
-        <f>VLOOKUP(A23, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>13.2</v>
       </c>
       <c r="Q23">
-        <f>VLOOKUP(E23,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R23">
-        <f>IF(D23="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="S23">
@@ -3118,71 +3118,71 @@
         <v>0.21</v>
       </c>
       <c r="T23">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U23">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U23">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V23">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V23">
+        <v>0.6784</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="33"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X23">
+        <f t="shared" si="34"/>
+        <v>0.71</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="35"/>
+        <v>2.8315099903999653E-4</v>
+      </c>
+      <c r="Z23">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W23">
-        <f>IF(H23="wet",$AN$6,$AN$7)</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X23">
-        <f>VLOOKUP(I23,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.71</v>
-      </c>
-      <c r="Y23">
-        <f>J23*K23*M23*X23*V23</f>
-        <v>4.1639852800000035E-3</v>
-      </c>
-      <c r="Z23">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA23">
-        <f>J23*K23*N23*Z23*V23</f>
-        <v>5.2372378239999996E-4</v>
+        <f t="shared" si="36"/>
+        <v>5.4941381214719997E-4</v>
       </c>
       <c r="AB23">
-        <f>C23*Y23*365</f>
-        <v>27.357383289600023</v>
+        <f t="shared" si="37"/>
+        <v>1.8603020636927772</v>
       </c>
       <c r="AC23">
-        <f>C23*AA23*365</f>
-        <v>3.4408652503679997</v>
+        <f t="shared" si="38"/>
+        <v>3.6096487458071036</v>
       </c>
       <c r="AD23">
-        <f>(AB23+AC23)*10^-3</f>
-        <v>3.0798248539968022E-2</v>
+        <f t="shared" si="39"/>
+        <v>5.4699508094998815E-3</v>
       </c>
       <c r="AE23">
-        <f>C23*P23*365</f>
+        <f t="shared" si="40"/>
         <v>86724</v>
       </c>
       <c r="AF23">
-        <f>AE23*W23*O23*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.81768342857142862</v>
       </c>
       <c r="AG23">
-        <f>AE23*S23</f>
+        <f t="shared" si="42"/>
         <v>18212.04</v>
       </c>
       <c r="AH23">
-        <f>AG23*Q23*O23*10^-3</f>
+        <f t="shared" si="43"/>
         <v>0.20033244000000003</v>
       </c>
       <c r="AI23">
-        <f>AE23*R23*T23</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="AJ23">
-        <f>AI23*U23*O23*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AM23" s="2" t="s">
@@ -3213,45 +3213,45 @@
         <v>98</v>
       </c>
       <c r="H24" t="str">
-        <f>VLOOKUP(G24,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>wet</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J24">
-        <f>VLOOKUP(A24, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>0.91</v>
       </c>
       <c r="K24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L24" t="s">
         <v>56</v>
       </c>
       <c r="M24">
-        <f>1-N24</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="29"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N24">
-        <f>IF(L24="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="17"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P24">
-        <f>VLOOKUP(A24, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>13.2</v>
       </c>
       <c r="Q24">
-        <f>VLOOKUP(E24,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>1.8E-3</v>
       </c>
       <c r="R24">
-        <f>IF(D24="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="S24">
@@ -3259,71 +3259,71 @@
         <v>0.21</v>
       </c>
       <c r="T24">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U24">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U24">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V24">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V24">
+        <v>0.6784</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="33"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X24">
+        <f t="shared" si="34"/>
+        <v>0.75</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" si="35"/>
+        <v>2.9910316799999635E-4</v>
+      </c>
+      <c r="Z24">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W24">
-        <f>IF(H24="wet",$AN$6,$AN$7)</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X24">
-        <f>VLOOKUP(I24,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.75</v>
-      </c>
-      <c r="Y24">
-        <f>J24*K24*M24*X24*V24</f>
-        <v>4.3985760000000039E-3</v>
-      </c>
-      <c r="Z24">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA24">
-        <f>J24*K24*N24*Z24*V24</f>
-        <v>5.2372378239999996E-4</v>
+        <f t="shared" si="36"/>
+        <v>5.4941381214719997E-4</v>
       </c>
       <c r="AB24">
-        <f>C24*Y24*365</f>
-        <v>30.504124560000029</v>
+        <f t="shared" si="37"/>
+        <v>2.0742804700799748</v>
       </c>
       <c r="AC24">
-        <f>C24*AA24*365</f>
-        <v>3.6320244309439995</v>
+        <f t="shared" si="38"/>
+        <v>3.8101847872408316</v>
       </c>
       <c r="AD24">
-        <f>(AB24+AC24)*10^-3</f>
-        <v>3.4136148990944033E-2</v>
+        <f t="shared" si="39"/>
+        <v>5.8844652573208072E-3</v>
       </c>
       <c r="AE24">
-        <f>C24*P24*365</f>
+        <f t="shared" si="40"/>
         <v>91542</v>
       </c>
       <c r="AF24">
-        <f>AE24*W24*O24*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.86311028571428583</v>
       </c>
       <c r="AG24">
-        <f>AE24*S24</f>
+        <f t="shared" si="42"/>
         <v>19223.82</v>
       </c>
       <c r="AH24">
-        <f>AG24*Q24*O24*10^-3</f>
+        <f t="shared" si="43"/>
         <v>5.4375948E-2</v>
       </c>
       <c r="AI24">
-        <f>AE24*R24*T24</f>
+        <f t="shared" si="44"/>
         <v>21970.079999999998</v>
       </c>
       <c r="AJ24">
-        <f>AI24*U24*O24*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0.37976852571428565</v>
       </c>
       <c r="AM24" s="2" t="s">
@@ -3355,45 +3355,45 @@
         <v>99</v>
       </c>
       <c r="H25" t="str">
-        <f>VLOOKUP(G25,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>wet</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>64</v>
       </c>
       <c r="J25">
-        <f>VLOOKUP(A25, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>2.73</v>
       </c>
       <c r="K25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L25" t="s">
         <v>56</v>
       </c>
       <c r="M25">
-        <f>1-N25</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="29"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N25">
-        <f>IF(L25="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="17"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P25">
-        <f>VLOOKUP(A25, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>39.5</v>
       </c>
       <c r="Q25">
-        <f>VLOOKUP(E25,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="R25">
-        <f>IF(D25="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="S25">
@@ -3401,71 +3401,71 @@
         <v>0.21</v>
       </c>
       <c r="T25">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U25">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U25">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V25">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V25">
+        <v>0.6784</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="33"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="34"/>
+        <v>0.8</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="35"/>
+        <v>9.5713013759998852E-4</v>
+      </c>
+      <c r="Z25">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W25">
-        <f>IF(H25="wet",$AN$6,$AN$7)</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="X25">
-        <f>VLOOKUP(I25,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.8</v>
-      </c>
-      <c r="Y25">
-        <f>J25*K25*M25*X25*V25</f>
-        <v>1.4075443200000013E-2</v>
-      </c>
-      <c r="Z25">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA25">
-        <f>J25*K25*N25*Z25*V25</f>
-        <v>1.5711713472E-3</v>
+        <f t="shared" si="36"/>
+        <v>1.6482414364416005E-3</v>
       </c>
       <c r="AB25">
-        <f>C25*Y25*365</f>
-        <v>102.75073536000009</v>
+        <f t="shared" si="37"/>
+        <v>6.987050004479916</v>
       </c>
       <c r="AC25">
-        <f>C25*AA25*365</f>
-        <v>11.46955083456</v>
+        <f t="shared" si="38"/>
+        <v>12.032162486023683</v>
       </c>
       <c r="AD25">
-        <f>(AB25+AC25)*10^-3</f>
-        <v>0.11422028619456009</v>
+        <f t="shared" si="39"/>
+        <v>1.90192124905036E-2</v>
       </c>
       <c r="AE25">
-        <f>C25*P25*365</f>
+        <f t="shared" si="40"/>
         <v>288350</v>
       </c>
       <c r="AF25">
-        <f>AE25*W25*O25*10^-3</f>
+        <f t="shared" si="41"/>
         <v>2.7187285714285716</v>
       </c>
       <c r="AG25">
-        <f>AE25*S25</f>
+        <f t="shared" si="42"/>
         <v>60553.5</v>
       </c>
       <c r="AH25">
-        <f>AG25*Q25*O25*10^-3</f>
+        <f t="shared" si="43"/>
         <v>0.27595094999999997</v>
       </c>
       <c r="AI25">
-        <f>AE25*R25*T25</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="AJ25">
-        <f>AI25*U25*O25*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AM25" s="2" t="s">
@@ -3497,45 +3497,45 @@
         <v>100</v>
       </c>
       <c r="H26" t="str">
-        <f>VLOOKUP(G26,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>dry</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="J26">
-        <f>VLOOKUP(A26, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>0.34</v>
       </c>
       <c r="K26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L26" t="s">
         <v>56</v>
       </c>
       <c r="M26">
-        <f>1-N26</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="29"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N26">
-        <f>IF(L26="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="17"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P26">
-        <f>VLOOKUP(A26, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>7</v>
       </c>
       <c r="Q26">
-        <f>VLOOKUP(E26,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="R26">
-        <f>IF(D26="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="S26">
@@ -3543,71 +3543,71 @@
         <v>0.21</v>
       </c>
       <c r="T26">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U26">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U26">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V26">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V26">
+        <v>0.6784</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="33"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="34"/>
+        <v>0.78</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="35"/>
+        <v>1.162229452799986E-4</v>
+      </c>
+      <c r="Z26">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W26">
-        <f>IF(H26="wet",$AN$6,$AN$7)</f>
-        <v>2E-3</v>
-      </c>
-      <c r="X26">
-        <f>VLOOKUP(I26,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.78</v>
-      </c>
-      <c r="Y26">
-        <f>J26*K26*M26*X26*V26</f>
-        <v>1.709160960000002E-3</v>
-      </c>
-      <c r="Z26">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA26">
-        <f>J26*K26*N26*Z26*V26</f>
-        <v>1.9567701760000002E-4</v>
+        <f t="shared" si="36"/>
+        <v>2.0527549025280004E-4</v>
       </c>
       <c r="AB26">
-        <f>C26*Y26*365</f>
-        <v>13.100718758400015</v>
+        <f t="shared" si="37"/>
+        <v>0.8908488755711893</v>
       </c>
       <c r="AC26">
-        <f>C26*AA26*365</f>
-        <v>1.4998643399039999</v>
+        <f t="shared" si="38"/>
+        <v>1.5734366327877123</v>
       </c>
       <c r="AD26">
-        <f>(AB26+AC26)*10^-3</f>
-        <v>1.4600583098304016E-2</v>
+        <f t="shared" si="39"/>
+        <v>2.4642855083589015E-3</v>
       </c>
       <c r="AE26">
-        <f>C26*P26*365</f>
+        <f t="shared" si="40"/>
         <v>53655</v>
       </c>
       <c r="AF26">
-        <f>AE26*W26*O26*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.16863</v>
       </c>
       <c r="AG26">
-        <f>AE26*S26</f>
+        <f t="shared" si="42"/>
         <v>11267.55</v>
       </c>
       <c r="AH26">
-        <f>AG26*Q26*O26*10^-3</f>
+        <f t="shared" si="43"/>
         <v>0.1416492</v>
       </c>
       <c r="AI26">
-        <f>AE26*R26*T26</f>
+        <f t="shared" si="44"/>
         <v>12877.199999999999</v>
       </c>
       <c r="AJ26">
-        <f>AI26*U26*O26*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0.22259159999999997</v>
       </c>
       <c r="AM26" s="2" t="s">
@@ -3639,45 +3639,45 @@
         <v>101</v>
       </c>
       <c r="H27" t="str">
-        <f>VLOOKUP(G27,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>dry</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>66</v>
       </c>
       <c r="J27">
-        <f>VLOOKUP(A27, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>2.73</v>
       </c>
       <c r="K27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L27" t="s">
         <v>56</v>
       </c>
       <c r="M27">
-        <f>1-N27</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="29"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N27">
-        <f>IF(L27="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="17"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P27">
-        <f>VLOOKUP(A27, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>39.5</v>
       </c>
       <c r="Q27">
-        <f>VLOOKUP(E27,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="R27">
-        <f>IF(D27="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="S27">
@@ -3685,71 +3685,71 @@
         <v>0.21</v>
       </c>
       <c r="T27">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U27">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U27">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V27">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V27">
+        <v>0.6784</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="33"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X27">
+        <f t="shared" si="34"/>
+        <v>0.74</v>
+      </c>
+      <c r="Y27">
+        <f t="shared" si="35"/>
+        <v>8.8534537727998931E-4</v>
+      </c>
+      <c r="Z27">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W27">
-        <f>IF(H27="wet",$AN$6,$AN$7)</f>
-        <v>2E-3</v>
-      </c>
-      <c r="X27">
-        <f>VLOOKUP(I27,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.74</v>
-      </c>
-      <c r="Y27">
-        <f>J27*K27*M27*X27*V27</f>
-        <v>1.3019784960000013E-2</v>
-      </c>
-      <c r="Z27">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA27">
-        <f>J27*K27*N27*Z27*V27</f>
-        <v>1.5711713472E-3</v>
+        <f t="shared" si="36"/>
+        <v>1.6482414364416005E-3</v>
       </c>
       <c r="AB27">
-        <f>C27*Y27*365</f>
-        <v>104.5488732288001</v>
+        <f t="shared" si="37"/>
+        <v>7.1093233795583135</v>
       </c>
       <c r="AC27">
-        <f>C27*AA27*365</f>
-        <v>12.616505918016001</v>
+        <f t="shared" si="38"/>
+        <v>13.235378734626051</v>
       </c>
       <c r="AD27">
-        <f>(AB27+AC27)*10^-3</f>
-        <v>0.11716537914681611</v>
+        <f t="shared" si="39"/>
+        <v>2.0344702114184366E-2</v>
       </c>
       <c r="AE27">
-        <f>C27*P27*365</f>
+        <f t="shared" si="40"/>
         <v>317185</v>
       </c>
       <c r="AF27">
-        <f>AE27*W27*O27*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.99686714285714295</v>
       </c>
       <c r="AG27">
-        <f>AE27*S27</f>
+        <f t="shared" si="42"/>
         <v>66608.849999999991</v>
       </c>
       <c r="AH27">
-        <f>AG27*Q27*O27*10^-3</f>
+        <f t="shared" si="43"/>
         <v>0.61755919499999989</v>
       </c>
       <c r="AI27">
-        <f>AE27*R27*T27</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="AJ27">
-        <f>AI27*U27*O27*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AM27" s="2" t="s">
@@ -3781,45 +3781,45 @@
         <v>102</v>
       </c>
       <c r="H28" t="str">
-        <f>VLOOKUP(G28,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>dry</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J28">
-        <f>VLOOKUP(A28, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>0.91</v>
       </c>
       <c r="K28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L28" t="s">
         <v>56</v>
       </c>
       <c r="M28">
-        <f>1-N28</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="29"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N28">
-        <f>IF(L28="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="17"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P28">
-        <f>VLOOKUP(A28, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>13.2</v>
       </c>
       <c r="Q28">
-        <f>VLOOKUP(E28,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="R28">
-        <f>IF(D28="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="S28">
@@ -3827,71 +3827,71 @@
         <v>0.21</v>
       </c>
       <c r="T28">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U28">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U28">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V28">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V28">
+        <v>0.6784</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="33"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X28">
+        <f t="shared" si="34"/>
+        <v>0.7</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" si="35"/>
+        <v>2.7916295679999655E-4</v>
+      </c>
+      <c r="Z28">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W28">
-        <f>IF(H28="wet",$AN$6,$AN$7)</f>
-        <v>2E-3</v>
-      </c>
-      <c r="X28">
-        <f>VLOOKUP(I28,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.7</v>
-      </c>
-      <c r="Y28">
-        <f>J28*K28*M28*X28*V28</f>
-        <v>4.1053376000000034E-3</v>
-      </c>
-      <c r="Z28">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA28">
-        <f>J28*K28*N28*Z28*V28</f>
-        <v>5.2372378239999996E-4</v>
+        <f t="shared" si="36"/>
+        <v>5.4941381214719997E-4</v>
       </c>
       <c r="AB28">
-        <f>C28*Y28*365</f>
-        <v>34.464309152000027</v>
+        <f t="shared" si="37"/>
+        <v>2.343573022335971</v>
       </c>
       <c r="AC28">
-        <f>C28*AA28*365</f>
-        <v>4.396661153248</v>
+        <f t="shared" si="38"/>
+        <v>4.6123289529757443</v>
       </c>
       <c r="AD28">
-        <f>(AB28+AC28)*10^-3</f>
-        <v>3.8860970305248023E-2</v>
+        <f t="shared" si="39"/>
+        <v>6.9559019753117146E-3</v>
       </c>
       <c r="AE28">
-        <f>C28*P28*365</f>
+        <f t="shared" si="40"/>
         <v>110813.99999999999</v>
       </c>
       <c r="AF28">
-        <f>AE28*W28*O28*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.34827257142857138</v>
       </c>
       <c r="AG28">
-        <f>AE28*S28</f>
+        <f t="shared" si="42"/>
         <v>23270.939999999995</v>
       </c>
       <c r="AH28">
-        <f>AG28*Q28*O28*10^-3</f>
+        <f t="shared" si="43"/>
         <v>0.25598033999999997</v>
       </c>
       <c r="AI28">
-        <f>AE28*R28*T28</f>
+        <f t="shared" si="44"/>
         <v>26595.359999999997</v>
       </c>
       <c r="AJ28">
-        <f>AI28*U28*O28*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0.45971979428571424</v>
       </c>
       <c r="AM28" s="2" t="s">
@@ -3923,45 +3923,45 @@
         <v>103</v>
       </c>
       <c r="H29" t="str">
-        <f>VLOOKUP(G29,$AR$31:$AS$40,2,FALSE)</f>
+        <f t="shared" si="27"/>
         <v>dry</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="J29">
-        <f>VLOOKUP(A29, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="28"/>
         <v>0.34</v>
       </c>
       <c r="K29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>0.19</v>
       </c>
       <c r="L29" t="s">
         <v>56</v>
       </c>
       <c r="M29">
-        <f>1-N29</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="29"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N29">
-        <f>IF(L29="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="17"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P29">
-        <f>VLOOKUP(A29, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="30"/>
         <v>7</v>
       </c>
       <c r="Q29">
-        <f>VLOOKUP(E29,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="31"/>
         <v>1.8E-3</v>
       </c>
       <c r="R29">
-        <f>IF(D29="yes", 1, 0)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="S29">
@@ -3969,71 +3969,71 @@
         <v>0.21</v>
       </c>
       <c r="T29">
+        <f t="shared" si="1"/>
+        <v>0.24</v>
+      </c>
+      <c r="U29">
         <f t="shared" si="2"/>
-        <v>0.24</v>
-      </c>
-      <c r="U29">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="V29">
         <f t="shared" si="3"/>
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="V29">
+        <v>0.6784</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="33"/>
+        <v>2E-3</v>
+      </c>
+      <c r="X29">
+        <f t="shared" si="34"/>
+        <v>0.74</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="35"/>
+        <v>1.1026279423999866E-4</v>
+      </c>
+      <c r="Z29">
         <f t="shared" si="4"/>
-        <v>0.6784</v>
-      </c>
-      <c r="W29">
-        <f>IF(H29="wet",$AN$6,$AN$7)</f>
-        <v>2E-3</v>
-      </c>
-      <c r="X29">
-        <f>VLOOKUP(I29,$AM$23:$AN$30,2,FALSE)</f>
-        <v>0.74</v>
-      </c>
-      <c r="Y29">
-        <f>J29*K29*M29*X29*V29</f>
-        <v>1.6215116800000018E-3</v>
-      </c>
-      <c r="Z29">
-        <f t="shared" si="5"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA29">
-        <f>J29*K29*N29*Z29*V29</f>
-        <v>1.9567701760000002E-4</v>
+        <f t="shared" si="36"/>
+        <v>2.0527549025280004E-4</v>
       </c>
       <c r="AB29">
-        <f>C29*Y29*365</f>
-        <v>14.204442316800016</v>
+        <f t="shared" si="37"/>
+        <v>0.96590207754238833</v>
       </c>
       <c r="AC29">
-        <f>C29*AA29*365</f>
-        <v>1.7141306741760001</v>
+        <f t="shared" si="38"/>
+        <v>1.7982132946145284</v>
       </c>
       <c r="AD29">
-        <f>(AB29+AC29)*10^-3</f>
-        <v>1.5918572990976015E-2</v>
+        <f t="shared" si="39"/>
+        <v>2.764115372156917E-3</v>
       </c>
       <c r="AE29">
-        <f>C29*P29*365</f>
+        <f t="shared" si="40"/>
         <v>61320</v>
       </c>
       <c r="AF29">
-        <f>AE29*W29*O29*10^-3</f>
+        <f t="shared" si="41"/>
         <v>0.19272</v>
       </c>
       <c r="AG29">
-        <f>AE29*S29</f>
+        <f t="shared" si="42"/>
         <v>12877.199999999999</v>
       </c>
       <c r="AH29">
-        <f>AG29*Q29*O29*10^-3</f>
+        <f t="shared" si="43"/>
         <v>3.6424079999999998E-2</v>
       </c>
       <c r="AI29">
-        <f>AE29*R29*T29</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="AJ29">
-        <f>AI29*U29*O29*10^-3</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AM29" s="2" t="s">
@@ -4207,7 +4207,7 @@
         <v>2.73</v>
       </c>
       <c r="K41">
-        <f t="shared" ref="K41:K60" si="27">$AQ$5</f>
+        <f t="shared" ref="K41:K59" si="46">$AQ$5</f>
         <v>0.19</v>
       </c>
       <c r="L41" t="s">
@@ -4215,14 +4215,14 @@
       </c>
       <c r="M41">
         <f>1-N41</f>
-        <v>5.0000000000000044E-2</v>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N41">
-        <f>IF(L41="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f>IF(L41="yes", 1, 0.9966)</f>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O41">
-        <f t="shared" ref="O41:O60" si="28">$AN$4</f>
+        <f t="shared" ref="O41:O59" si="47">$AN$4</f>
         <v>1.5714285714285714</v>
       </c>
       <c r="P41">
@@ -4238,15 +4238,15 @@
         <v>1</v>
       </c>
       <c r="T41">
-        <f t="shared" ref="T41:T60" si="29">$AQ$3</f>
+        <f t="shared" ref="T41:T59" si="48">$AQ$3</f>
         <v>0.24</v>
       </c>
       <c r="U41">
-        <f t="shared" ref="U41:U60" si="30">$AQ$4</f>
+        <f t="shared" ref="U41:U59" si="49">$AQ$4</f>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V41">
-        <f t="shared" ref="V41:V60" si="31">$AN$5</f>
+        <f t="shared" ref="V41:V59" si="50">$AN$5</f>
         <v>0.6784</v>
       </c>
       <c r="X41">
@@ -4255,27 +4255,27 @@
       </c>
       <c r="Y41">
         <f>J41*K41*M41*X41*V41</f>
-        <v>1.1612240640000012E-2</v>
+        <v>7.8963236351999055E-4</v>
       </c>
       <c r="Z41">
-        <f t="shared" ref="Z41:Z60" si="32">$AM$33</f>
+        <f t="shared" ref="Z41:Z59" si="51">$AM$33</f>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA41">
         <f>J41*K41*N41*Z41*V41</f>
-        <v>1.5711713472E-3</v>
+        <v>1.6482414364416005E-3</v>
       </c>
       <c r="AB41">
         <f>C41*Y41*365</f>
-        <v>21.192339168000025</v>
+        <v>1.4410790634239827</v>
       </c>
       <c r="AC41">
         <f>C41*AA41*365</f>
-        <v>2.8673877086399999</v>
+        <v>3.0080406215059208</v>
       </c>
       <c r="AD41">
         <f>(AB41+AC41)*10^-3</f>
-        <v>2.4059726876640024E-2</v>
+        <v>4.4491196849299032E-3</v>
       </c>
       <c r="AM41">
         <v>14</v>
@@ -4311,7 +4311,7 @@
         <v>2.73</v>
       </c>
       <c r="K42">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L42" t="s">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="M42">
         <f>1-N42</f>
-        <v>5.0000000000000044E-2</v>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N42">
-        <f>IF(L42="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" ref="N42:N59" si="52">IF(L42="yes", 1, 0.9966)</f>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O42">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P42">
@@ -4342,44 +4342,44 @@
         <v>0</v>
       </c>
       <c r="T42">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U42">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V42">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X42">
-        <f t="shared" ref="X42:X60" si="33">VLOOKUP(F42, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" ref="X42:X47" si="53">VLOOKUP(F42, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.68</v>
       </c>
       <c r="Y42">
         <f>J42*K42*M42*X42*V42</f>
-        <v>1.1964126720000011E-2</v>
+        <v>8.1356061695999021E-4</v>
       </c>
       <c r="Z42">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA42">
         <f>J42*K42*N42*Z42*V42</f>
-        <v>1.5711713472E-3</v>
+        <v>1.6482414364416005E-3</v>
       </c>
       <c r="AB42">
         <f>C42*Y42*365</f>
-        <v>26.201437516800027</v>
+        <v>1.7816977511423786</v>
       </c>
       <c r="AC42">
         <f>C42*AA42*365</f>
-        <v>3.4408652503679997</v>
+        <v>3.6096487458071049</v>
       </c>
       <c r="AD42">
         <f>(AB42+AC42)*10^-3</f>
-        <v>2.9642302767168026E-2</v>
+        <v>5.3913464969494842E-3</v>
       </c>
       <c r="AM42">
         <v>15</v>
@@ -4411,79 +4411,79 @@
         <v>65</v>
       </c>
       <c r="J43">
-        <f t="shared" ref="J43:J60" si="34">VLOOKUP(A43, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" ref="J43:J47" si="54">VLOOKUP(A43, $AM$11:$AN$18,2,FALSE)</f>
         <v>2.73</v>
       </c>
       <c r="K43">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L43" t="s">
         <v>56</v>
       </c>
       <c r="M43">
-        <f t="shared" ref="M43:M60" si="35">1-N43</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="M43:M47" si="55">1-N43</f>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N43">
-        <f t="shared" ref="N43:N60" si="36">IF(L43="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="52"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O43">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P43">
-        <f t="shared" ref="P43:P60" si="37">VLOOKUP(A43, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" ref="P43:P47" si="56">VLOOKUP(A43, $AM$11:$AO$18,3,FALSE)</f>
         <v>39.5</v>
       </c>
       <c r="Q43">
-        <f t="shared" ref="Q43:Q60" si="38">VLOOKUP(E43,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" ref="Q43:Q47" si="57">VLOOKUP(E43,$AR$10:$AS$22,2,FALSE)</f>
         <v>1.8E-3</v>
       </c>
       <c r="R43">
-        <f t="shared" ref="R43:R60" si="39">IF(D43="yes", 1, 0)</f>
+        <f t="shared" ref="R43:R47" si="58">IF(D43="yes", 1, 0)</f>
         <v>1</v>
       </c>
       <c r="T43">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U43">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V43">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X43">
-        <f t="shared" si="33"/>
+        <f t="shared" si="53"/>
         <v>0.7</v>
       </c>
       <c r="Y43">
-        <f t="shared" ref="Y43:Y60" si="40">J43*K43*M43*X43*V43</f>
-        <v>1.231601280000001E-2</v>
+        <f t="shared" ref="Y43:Y47" si="59">J43*K43*M43*X43*V43</f>
+        <v>8.3748887039998988E-4</v>
       </c>
       <c r="Z43">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA43">
-        <f t="shared" ref="AA43:AA60" si="41">J43*K43*N43*Z43*V43</f>
-        <v>1.5711713472E-3</v>
+        <f t="shared" ref="AA43:AA47" si="60">J43*K43*N43*Z43*V43</f>
+        <v>1.6482414364416005E-3</v>
       </c>
       <c r="AB43">
-        <f t="shared" ref="AB43:AB60" si="42">C43*Y43*365</f>
-        <v>31.467412704000026</v>
+        <f t="shared" ref="AB43:AB47" si="61">C43*Y43*365</f>
+        <v>2.1397840638719741</v>
       </c>
       <c r="AC43">
-        <f t="shared" ref="AC43:AC60" si="43">C43*AA43*365</f>
-        <v>4.0143427920960004</v>
+        <f t="shared" ref="AC43:AC47" si="62">C43*AA43*365</f>
+        <v>4.2112568701082891</v>
       </c>
       <c r="AD43">
-        <f t="shared" ref="AD43:AD60" si="44">(AB43+AC43)*10^-3</f>
-        <v>3.5481755496096029E-2</v>
+        <f t="shared" ref="AD43:AD47" si="63">(AB43+AC43)*10^-3</f>
+        <v>6.3510409339802634E-3</v>
       </c>
       <c r="AM43">
         <v>16</v>
@@ -4515,79 +4515,79 @@
         <v>65</v>
       </c>
       <c r="J44">
-        <f t="shared" si="34"/>
+        <f t="shared" si="54"/>
         <v>2.73</v>
       </c>
       <c r="K44">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L44" t="s">
         <v>56</v>
       </c>
       <c r="M44">
-        <f t="shared" si="35"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="55"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N44">
-        <f t="shared" si="36"/>
-        <v>0.95</v>
+        <f t="shared" si="52"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O44">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P44">
-        <f t="shared" si="37"/>
+        <f t="shared" si="56"/>
         <v>39.5</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="38"/>
+        <f t="shared" si="57"/>
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="R44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="T44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U44">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X44">
-        <f t="shared" si="33"/>
+        <f t="shared" si="53"/>
         <v>0.71</v>
       </c>
       <c r="Y44">
-        <f t="shared" si="40"/>
-        <v>1.2491955840000011E-2</v>
+        <f t="shared" si="59"/>
+        <v>8.4945299711998976E-4</v>
       </c>
       <c r="Z44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA44">
-        <f t="shared" si="41"/>
-        <v>1.5711713472E-3</v>
+        <f t="shared" si="60"/>
+        <v>1.6482414364416005E-3</v>
       </c>
       <c r="AB44">
-        <f t="shared" si="42"/>
-        <v>36.476511052800035</v>
+        <f t="shared" si="61"/>
+        <v>2.4804027515903702</v>
       </c>
       <c r="AC44">
-        <f t="shared" si="43"/>
-        <v>4.5878203338240002</v>
+        <f t="shared" si="62"/>
+        <v>4.8128649944094732</v>
       </c>
       <c r="AD44">
-        <f t="shared" si="44"/>
-        <v>4.1064331386624034E-2</v>
+        <f t="shared" si="63"/>
+        <v>7.2932677459998435E-3</v>
       </c>
       <c r="AM44">
         <v>17</v>
@@ -4619,79 +4619,79 @@
         <v>65</v>
       </c>
       <c r="J45">
-        <f t="shared" si="34"/>
+        <f t="shared" si="54"/>
         <v>0.34</v>
       </c>
       <c r="K45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L45" t="s">
         <v>56</v>
       </c>
       <c r="M45">
-        <f t="shared" si="35"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="55"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N45">
-        <f t="shared" si="36"/>
-        <v>0.95</v>
+        <f t="shared" si="52"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O45">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="56"/>
         <v>7</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="57"/>
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="R45">
-        <f t="shared" si="39"/>
+        <f t="shared" si="58"/>
         <v>1</v>
       </c>
       <c r="T45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U45">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V45">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X45">
-        <f t="shared" si="33"/>
+        <f t="shared" si="53"/>
         <v>0.73</v>
       </c>
       <c r="Y45">
-        <f t="shared" si="40"/>
-        <v>1.5995993600000015E-3</v>
+        <f t="shared" si="59"/>
+        <v>1.0877275647999869E-4</v>
       </c>
       <c r="Z45">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA45">
-        <f t="shared" si="41"/>
-        <v>1.9567701760000002E-4</v>
+        <f t="shared" si="60"/>
+        <v>2.0527549025280004E-4</v>
       </c>
       <c r="AB45">
-        <f t="shared" si="42"/>
-        <v>5.254683897600005</v>
+        <f t="shared" si="61"/>
+        <v>0.35731850503679569</v>
       </c>
       <c r="AC45">
-        <f t="shared" si="43"/>
-        <v>0.64279900281600011</v>
+        <f t="shared" si="62"/>
+        <v>0.6743299854804482</v>
       </c>
       <c r="AD45">
-        <f t="shared" si="44"/>
-        <v>5.8974829004160047E-3</v>
+        <f t="shared" si="63"/>
+        <v>1.0316484905172438E-3</v>
       </c>
       <c r="AM45">
         <v>18</v>
@@ -4714,7 +4714,7 @@
         <v>56</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F46">
         <v>15</v>
@@ -4723,79 +4723,79 @@
         <v>26</v>
       </c>
       <c r="J46">
-        <f t="shared" si="34"/>
+        <f t="shared" si="54"/>
         <v>0.34</v>
       </c>
       <c r="K46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L46" t="s">
         <v>56</v>
       </c>
       <c r="M46">
-        <f t="shared" si="35"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="55"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N46">
-        <f t="shared" si="36"/>
-        <v>0.95</v>
+        <f t="shared" si="52"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="56"/>
         <v>7</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="38"/>
-        <v>1.9900000000000001E-2</v>
+        <f t="shared" si="57"/>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="R46">
-        <f t="shared" si="39"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="T46">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V46">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X46">
-        <f t="shared" si="33"/>
+        <f t="shared" si="53"/>
         <v>0.74</v>
       </c>
       <c r="Y46">
-        <f t="shared" si="40"/>
-        <v>1.6215116800000018E-3</v>
+        <f t="shared" si="59"/>
+        <v>1.1026279423999866E-4</v>
       </c>
       <c r="Z46">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA46">
-        <f t="shared" si="41"/>
-        <v>1.9567701760000002E-4</v>
+        <f t="shared" si="60"/>
+        <v>2.0527549025280004E-4</v>
       </c>
       <c r="AB46">
-        <f t="shared" si="42"/>
-        <v>5.9185176320000075</v>
+        <f t="shared" si="61"/>
+        <v>0.40245919897599514</v>
       </c>
       <c r="AC46">
-        <f t="shared" si="43"/>
-        <v>0.71422111424000012</v>
+        <f t="shared" si="62"/>
+        <v>0.74925553942272027</v>
       </c>
       <c r="AD46">
-        <f t="shared" si="44"/>
-        <v>6.6327387462400073E-3</v>
+        <f t="shared" si="63"/>
+        <v>1.1517147383987155E-3</v>
       </c>
       <c r="AM46">
         <v>19</v>
@@ -4818,7 +4818,7 @@
         <v>55</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F47">
         <v>16</v>
@@ -4827,79 +4827,79 @@
         <v>63</v>
       </c>
       <c r="J47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="54"/>
         <v>0.34</v>
       </c>
       <c r="K47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L47" t="s">
         <v>56</v>
       </c>
       <c r="M47">
-        <f t="shared" si="35"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="55"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N47">
-        <f t="shared" si="36"/>
-        <v>0.95</v>
+        <f t="shared" si="52"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P47">
-        <f t="shared" si="37"/>
+        <f t="shared" si="56"/>
         <v>7</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="38"/>
-        <v>5.3E-3</v>
+        <f t="shared" si="57"/>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="R47">
-        <f t="shared" si="39"/>
+        <f t="shared" si="58"/>
         <v>1</v>
       </c>
       <c r="T47">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V47">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="53"/>
         <v>0.75</v>
       </c>
       <c r="Y47">
-        <f t="shared" si="40"/>
-        <v>1.6434240000000016E-3</v>
+        <f t="shared" si="59"/>
+        <v>1.1175283199999866E-4</v>
       </c>
       <c r="Z47">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA47">
-        <f t="shared" si="41"/>
-        <v>1.9567701760000002E-4</v>
+        <f t="shared" si="60"/>
+        <v>2.0527549025280004E-4</v>
       </c>
       <c r="AB47">
-        <f t="shared" si="42"/>
-        <v>6.5983473600000062</v>
+        <f t="shared" si="61"/>
+        <v>0.44868762047999466</v>
       </c>
       <c r="AC47">
-        <f t="shared" si="43"/>
-        <v>0.78564322566400013</v>
+        <f t="shared" si="62"/>
+        <v>0.82418109336499212</v>
       </c>
       <c r="AD47">
-        <f t="shared" si="44"/>
-        <v>7.383990585664006E-3</v>
+        <f t="shared" si="63"/>
+        <v>1.2728687138449867E-3</v>
       </c>
       <c r="AM47">
         <v>20</v>
@@ -4922,7 +4922,7 @@
         <v>55</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F48">
         <v>18</v>
@@ -4931,79 +4931,79 @@
         <v>65</v>
       </c>
       <c r="J48">
-        <f>VLOOKUP(A48, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" ref="J48:J59" si="64">VLOOKUP(A48, $AM$11:$AN$18,2,FALSE)</f>
         <v>0.34</v>
       </c>
       <c r="K48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L48" t="s">
         <v>56</v>
       </c>
       <c r="M48">
-        <f>1-N48</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="M48:M59" si="65">1-N48</f>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N48">
-        <f>IF(L48="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="52"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O48">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P48">
-        <f>VLOOKUP(A48, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" ref="P48:P59" si="66">VLOOKUP(A48, $AM$11:$AO$18,3,FALSE)</f>
         <v>7</v>
       </c>
       <c r="Q48">
-        <f>VLOOKUP(E48,$AR$10:$AS$22,2,FALSE)</f>
-        <v>2.5999999999999999E-3</v>
+        <f t="shared" ref="Q48:Q59" si="67">VLOOKUP(E48,$AR$10:$AS$22,2,FALSE)</f>
+        <v>1.8E-3</v>
       </c>
       <c r="R48">
-        <f>IF(D48="yes", 1, 0)</f>
+        <f t="shared" ref="R48:R59" si="68">IF(D48="yes", 1, 0)</f>
         <v>1</v>
       </c>
       <c r="T48">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U48">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V48">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X48">
-        <f>VLOOKUP(F48, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" ref="X48:X59" si="69">VLOOKUP(F48, $AM$37:$AN$55, 2, FALSE)</f>
         <v>0.77</v>
       </c>
       <c r="Y48">
-        <f>J48*K48*M48*X48*V48</f>
-        <v>1.6872486400000017E-3</v>
+        <f t="shared" ref="Y48:Y59" si="70">J48*K48*M48*X48*V48</f>
+        <v>1.1473290751999861E-4</v>
       </c>
       <c r="Z48">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA48">
-        <f>J48*K48*N48*Z48*V48</f>
-        <v>1.9567701760000002E-4</v>
+        <f t="shared" ref="AA48:AA59" si="71">J48*K48*N48*Z48*V48</f>
+        <v>2.0527549025280004E-4</v>
       </c>
       <c r="AB48">
-        <f>C48*Y48*365</f>
-        <v>8.0059947968000085</v>
+        <f t="shared" ref="AB48:AB59" si="72">C48*Y48*365</f>
+        <v>0.54440764618239346</v>
       </c>
       <c r="AC48">
-        <f>C48*AA48*365</f>
-        <v>0.92848744851200005</v>
+        <f t="shared" ref="AC48:AC59" si="73">C48*AA48*365</f>
+        <v>0.97403220124953627</v>
       </c>
       <c r="AD48">
-        <f>(AB48+AC48)*10^-3</f>
-        <v>8.9344822453120091E-3</v>
+        <f t="shared" ref="AD48:AD59" si="74">(AB48+AC48)*10^-3</f>
+        <v>1.5184398474319299E-3</v>
       </c>
       <c r="AM48">
         <v>21</v>
@@ -5026,7 +5026,7 @@
         <v>56</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F49">
         <v>19</v>
@@ -5035,79 +5035,79 @@
         <v>66</v>
       </c>
       <c r="J49">
-        <f>VLOOKUP(A49, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>0.34</v>
       </c>
       <c r="K49">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L49" t="s">
         <v>56</v>
       </c>
       <c r="M49">
-        <f>1-N49</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="65"/>
+        <v>3.3999999999999586E-3</v>
       </c>
       <c r="N49">
-        <f>IF(L49="yes", 1, 0.95)</f>
-        <v>0.95</v>
+        <f t="shared" si="52"/>
+        <v>0.99660000000000004</v>
       </c>
       <c r="O49">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P49">
-        <f>VLOOKUP(A49, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>7</v>
       </c>
       <c r="Q49">
-        <f>VLOOKUP(E49,$AR$10:$AS$22,2,FALSE)</f>
-        <v>3.0000000000000001E-3</v>
+        <f t="shared" si="67"/>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="R49">
-        <f>IF(D49="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="T49">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U49">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V49">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X49">
-        <f>VLOOKUP(F49, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.77</v>
       </c>
       <c r="Y49">
-        <f>J49*K49*M49*X49*V49</f>
-        <v>1.6872486400000017E-3</v>
+        <f t="shared" si="70"/>
+        <v>1.1473290751999861E-4</v>
       </c>
       <c r="Z49">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA49">
-        <f>J49*K49*N49*Z49*V49</f>
-        <v>1.9567701760000002E-4</v>
+        <f t="shared" si="71"/>
+        <v>2.0527549025280004E-4</v>
       </c>
       <c r="AB49">
-        <f>C49*Y49*365</f>
-        <v>8.6218405504000089</v>
+        <f t="shared" si="72"/>
+        <v>0.58628515742719289</v>
       </c>
       <c r="AC49">
-        <f>C49*AA49*365</f>
-        <v>0.99990955993600006</v>
+        <f t="shared" si="73"/>
+        <v>1.0489577551918081</v>
       </c>
       <c r="AD49">
-        <f>(AB49+AC49)*10^-3</f>
-        <v>9.6217501103360095E-3</v>
+        <f t="shared" si="74"/>
+        <v>1.6352429126190011E-3</v>
       </c>
       <c r="AM49">
         <v>22</v>
@@ -5130,7 +5130,7 @@
         <v>55</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F50">
         <v>20</v>
@@ -5139,78 +5139,78 @@
         <v>67</v>
       </c>
       <c r="J50">
-        <f>VLOOKUP(A50, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>0.34</v>
       </c>
       <c r="K50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L50" t="s">
         <v>55</v>
       </c>
       <c r="M50">
-        <f>1-N50</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N50">
-        <f>IF(L50="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P50">
-        <f>VLOOKUP(A50, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>7</v>
       </c>
       <c r="Q50">
-        <f>VLOOKUP(E50,$AR$10:$AS$22,2,FALSE)</f>
-        <v>5.0000000000000001E-3</v>
+        <f t="shared" si="67"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="R50">
-        <f>IF(D50="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="T50">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U50">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V50">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X50">
-        <f>VLOOKUP(F50, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.78</v>
       </c>
       <c r="Y50">
-        <f>J50*K50*M50*X50*V50</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z50">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA50">
-        <f>J50*K50*N50*Z50*V50</f>
+        <f t="shared" si="71"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB50">
-        <f>C50*Y50*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC50">
-        <f>C50*AA50*365</f>
+        <f t="shared" si="73"/>
         <v>1.1277175488000002</v>
       </c>
       <c r="AD50">
-        <f>(AB50+AC50)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>1.1277175488000003E-3</v>
       </c>
       <c r="AM50">
@@ -5234,7 +5234,7 @@
         <v>56</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F51">
         <v>21</v>
@@ -5243,78 +5243,78 @@
         <v>68</v>
       </c>
       <c r="J51">
-        <f>VLOOKUP(A51, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>0.91</v>
       </c>
       <c r="K51">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L51" t="s">
         <v>55</v>
       </c>
       <c r="M51">
-        <f>1-N51</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N51">
-        <f>IF(L51="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O51">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P51">
-        <f>VLOOKUP(A51, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>13.2</v>
       </c>
       <c r="Q51">
-        <f>VLOOKUP(E51,$AR$10:$AS$22,2,FALSE)</f>
-        <v>2.5999999999999999E-3</v>
+        <f t="shared" si="67"/>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="R51">
-        <f>IF(D51="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="T51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U51">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V51">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X51">
-        <f>VLOOKUP(F51, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.78</v>
       </c>
       <c r="Y51">
-        <f>J51*K51*M51*X51*V51</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z51">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA51">
-        <f>J51*K51*N51*Z51*V51</f>
+        <f t="shared" si="71"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB51">
-        <f>C51*Y51*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC51">
-        <f>C51*AA51*365</f>
+        <f t="shared" si="73"/>
         <v>3.21952304128</v>
       </c>
       <c r="AD51">
-        <f>(AB51+AC51)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>3.21952304128E-3</v>
       </c>
       <c r="AM51">
@@ -5338,7 +5338,7 @@
         <v>55</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F52">
         <v>22</v>
@@ -5347,78 +5347,78 @@
         <v>69</v>
       </c>
       <c r="J52">
-        <f>VLOOKUP(A52, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>0.91</v>
       </c>
       <c r="K52">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L52" t="s">
         <v>55</v>
       </c>
       <c r="M52">
-        <f>1-N52</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N52">
-        <f>IF(L52="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P52">
-        <f>VLOOKUP(A52, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>13.2</v>
       </c>
       <c r="Q52">
-        <f>VLOOKUP(E52,$AR$10:$AS$22,2,FALSE)</f>
-        <v>1.8E-3</v>
+        <f t="shared" si="67"/>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="R52">
-        <f>IF(D52="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="T52">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U52">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V52">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X52">
-        <f>VLOOKUP(F52, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.78</v>
       </c>
       <c r="Y52">
-        <f>J52*K52*M52*X52*V52</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z52">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA52">
-        <f>J52*K52*N52*Z52*V52</f>
+        <f t="shared" si="71"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB52">
-        <f>C52*Y52*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC52">
-        <f>C52*AA52*365</f>
+        <f t="shared" si="73"/>
         <v>3.4207432313599999</v>
       </c>
       <c r="AD52">
-        <f>(AB52+AC52)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>3.4207432313600001E-3</v>
       </c>
       <c r="AM52">
@@ -5451,78 +5451,78 @@
         <v>26</v>
       </c>
       <c r="J53">
-        <f>VLOOKUP(A53, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>0.91</v>
       </c>
       <c r="K53">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L53" t="s">
         <v>55</v>
       </c>
       <c r="M53">
-        <f>1-N53</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N53">
-        <f>IF(L53="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O53">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P53">
-        <f>VLOOKUP(A53, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>13.2</v>
       </c>
       <c r="Q53">
-        <f>VLOOKUP(E53,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="67"/>
         <v>1.8E-3</v>
       </c>
       <c r="R53">
-        <f>IF(D53="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="T53">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U53">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V53">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X53">
-        <f>VLOOKUP(F53, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.79</v>
       </c>
       <c r="Y53">
-        <f>J53*K53*M53*X53*V53</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z53">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA53">
-        <f>J53*K53*N53*Z53*V53</f>
+        <f t="shared" si="71"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB53">
-        <f>C53*Y53*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC53">
-        <f>C53*AA53*365</f>
+        <f t="shared" si="73"/>
         <v>3.6219634214399998</v>
       </c>
       <c r="AD53">
-        <f>(AB53+AC53)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>3.6219634214399998E-3</v>
       </c>
       <c r="AM53">
@@ -5555,78 +5555,78 @@
         <v>63</v>
       </c>
       <c r="J54">
-        <f>VLOOKUP(A54, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>0.91</v>
       </c>
       <c r="K54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L54" t="s">
         <v>55</v>
       </c>
       <c r="M54">
-        <f>1-N54</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N54">
-        <f>IF(L54="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O54">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P54">
-        <f>VLOOKUP(A54, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>13.2</v>
       </c>
       <c r="Q54">
-        <f>VLOOKUP(E54,$AR$10:$AS$22,2,FALSE)</f>
+        <f t="shared" si="67"/>
         <v>2.8999999999999998E-3</v>
       </c>
       <c r="R54">
-        <f>IF(D54="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="T54">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U54">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V54">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X54">
-        <f>VLOOKUP(F54, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.79</v>
       </c>
       <c r="Y54">
-        <f>J54*K54*M54*X54*V54</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z54">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA54">
-        <f>J54*K54*N54*Z54*V54</f>
+        <f t="shared" si="71"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB54">
-        <f>C54*Y54*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC54">
-        <f>C54*AA54*365</f>
+        <f t="shared" si="73"/>
         <v>3.8231836115200006</v>
       </c>
       <c r="AD54">
-        <f>(AB54+AC54)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>3.8231836115200008E-3</v>
       </c>
       <c r="AM54">
@@ -5650,7 +5650,7 @@
         <v>56</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F55">
         <v>25</v>
@@ -5659,78 +5659,78 @@
         <v>64</v>
       </c>
       <c r="J55">
-        <f>VLOOKUP(A55, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>2.73</v>
       </c>
       <c r="K55">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L55" t="s">
         <v>55</v>
       </c>
       <c r="M55">
-        <f>1-N55</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N55">
-        <f>IF(L55="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O55">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P55">
-        <f>VLOOKUP(A55, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>39.5</v>
       </c>
       <c r="Q55">
-        <f>VLOOKUP(E55,$AR$10:$AS$22,2,FALSE)</f>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="67"/>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="R55">
-        <f>IF(D55="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="T55">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U55">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V55">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X55">
-        <f>VLOOKUP(F55, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.79</v>
       </c>
       <c r="Y55">
-        <f>J55*K55*M55*X55*V55</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z55">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA55">
-        <f>J55*K55*N55*Z55*V55</f>
+        <f t="shared" si="71"/>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB55">
-        <f>C55*Y55*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC55">
-        <f>C55*AA55*365</f>
+        <f t="shared" si="73"/>
         <v>12.0732114048</v>
       </c>
       <c r="AD55">
-        <f>(AB55+AC55)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>1.2073211404800001E-2</v>
       </c>
       <c r="AM55" t="s">
@@ -5754,7 +5754,7 @@
         <v>55</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F56">
         <v>26</v>
@@ -5763,78 +5763,78 @@
         <v>65</v>
       </c>
       <c r="J56">
-        <f>VLOOKUP(A56, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>0.34</v>
       </c>
       <c r="K56">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L56" t="s">
         <v>55</v>
       </c>
       <c r="M56">
-        <f>1-N56</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N56">
-        <f>IF(L56="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O56">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P56">
-        <f>VLOOKUP(A56, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>7</v>
       </c>
       <c r="Q56">
-        <f>VLOOKUP(E56,$AR$10:$AS$22,2,FALSE)</f>
-        <v>1.9900000000000001E-2</v>
+        <f t="shared" si="67"/>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="R56">
-        <f>IF(D56="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="T56">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U56">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V56">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X56">
-        <f>VLOOKUP(F56, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.79</v>
       </c>
       <c r="Y56">
-        <f>J56*K56*M56*X56*V56</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z56">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA56">
-        <f>J56*K56*N56*Z56*V56</f>
+        <f t="shared" si="71"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB56">
-        <f>C56*Y56*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC56">
-        <f>C56*AA56*365</f>
+        <f t="shared" si="73"/>
         <v>1.57880456832</v>
       </c>
       <c r="AD56">
-        <f>(AB56+AC56)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>1.5788045683200001E-3</v>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
         <v>56</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F57">
         <v>27</v>
@@ -5861,78 +5861,78 @@
         <v>66</v>
       </c>
       <c r="J57">
-        <f>VLOOKUP(A57, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>2.73</v>
       </c>
       <c r="K57">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L57" t="s">
         <v>55</v>
       </c>
       <c r="M57">
-        <f>1-N57</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N57">
-        <f>IF(L57="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O57">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P57">
-        <f>VLOOKUP(A57, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>39.5</v>
       </c>
       <c r="Q57">
-        <f>VLOOKUP(E57,$AR$10:$AS$22,2,FALSE)</f>
-        <v>5.3E-3</v>
+        <f t="shared" si="67"/>
+        <v>1.8E-3</v>
       </c>
       <c r="R57">
-        <f>IF(D57="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="T57">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U57">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V57">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X57">
-        <f>VLOOKUP(F57, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.8</v>
       </c>
       <c r="Y57">
-        <f>J57*K57*M57*X57*V57</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z57">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA57">
-        <f>J57*K57*N57*Z57*V57</f>
+        <f t="shared" si="71"/>
         <v>1.6538645760000002E-3</v>
       </c>
       <c r="AB57">
-        <f>C57*Y57*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC57">
-        <f>C57*AA57*365</f>
+        <f t="shared" si="73"/>
         <v>13.28053254528</v>
       </c>
       <c r="AD57">
-        <f>(AB57+AC57)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>1.3280532545279999E-2</v>
       </c>
     </row>
@@ -5950,7 +5950,7 @@
         <v>55</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F58" t="s">
         <v>91</v>
@@ -5959,78 +5959,78 @@
         <v>67</v>
       </c>
       <c r="J58">
-        <f>VLOOKUP(A58, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>0.91</v>
       </c>
       <c r="K58">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L58" t="s">
         <v>55</v>
       </c>
       <c r="M58">
-        <f>1-N58</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N58">
-        <f>IF(L58="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O58">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P58">
-        <f>VLOOKUP(A58, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>13.2</v>
       </c>
       <c r="Q58">
-        <f>VLOOKUP(E58,$AR$10:$AS$22,2,FALSE)</f>
-        <v>6.4000000000000003E-3</v>
+        <f t="shared" si="67"/>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="R58">
-        <f>IF(D58="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="T58">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U58">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V58">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X58">
-        <f>VLOOKUP(F58, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.8</v>
       </c>
       <c r="Y58">
-        <f>J58*K58*M58*X58*V58</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z58">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA58">
-        <f>J58*K58*N58*Z58*V58</f>
+        <f t="shared" si="71"/>
         <v>5.5128819200000003E-4</v>
       </c>
       <c r="AB58">
-        <f>C58*Y58*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC58">
-        <f>C58*AA58*365</f>
+        <f t="shared" si="73"/>
         <v>4.6280643718399999</v>
       </c>
       <c r="AD58">
-        <f>(AB58+AC58)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>4.6280643718400001E-3</v>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
         <v>56</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F59">
         <v>20</v>
@@ -6057,78 +6057,78 @@
         <v>68</v>
       </c>
       <c r="J59">
-        <f>VLOOKUP(A59, $AM$11:$AN$18,2,FALSE)</f>
+        <f t="shared" si="64"/>
         <v>0.34</v>
       </c>
       <c r="K59">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>0.19</v>
       </c>
       <c r="L59" t="s">
         <v>55</v>
       </c>
       <c r="M59">
-        <f>1-N59</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="N59">
-        <f>IF(L59="yes", 1, 0.95)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="O59">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>1.5714285714285714</v>
       </c>
       <c r="P59">
-        <f>VLOOKUP(A59, $AM$11:$AO$18,3,FALSE)</f>
+        <f t="shared" si="66"/>
         <v>7</v>
       </c>
       <c r="Q59">
-        <f>VLOOKUP(E59,$AR$10:$AS$22,2,FALSE)</f>
-        <v>2.5999999999999999E-3</v>
+        <f t="shared" si="67"/>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="R59">
-        <f>IF(D59="yes", 1, 0)</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="T59">
-        <f t="shared" si="29"/>
+        <f t="shared" si="48"/>
         <v>0.24</v>
       </c>
       <c r="U59">
-        <f t="shared" si="30"/>
+        <f t="shared" si="49"/>
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="V59">
-        <f t="shared" si="31"/>
+        <f t="shared" si="50"/>
         <v>0.6784</v>
       </c>
       <c r="X59">
-        <f>VLOOKUP(F59, $AM$37:$AN$55, 2, FALSE)</f>
+        <f t="shared" si="69"/>
         <v>0.78</v>
       </c>
       <c r="Y59">
-        <f>J59*K59*M59*X59*V59</f>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Z59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="51"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="AA59">
-        <f>J59*K59*N59*Z59*V59</f>
+        <f t="shared" si="71"/>
         <v>2.0597580800000003E-4</v>
       </c>
       <c r="AB59">
-        <f>C59*Y59*365</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC59">
-        <f>C59*AA59*365</f>
+        <f t="shared" si="73"/>
         <v>1.8043480780800005</v>
       </c>
       <c r="AD59">
-        <f>(AB59+AC59)*10^-3</f>
+        <f t="shared" si="74"/>
         <v>1.8043480780800005E-3</v>
       </c>
     </row>

--- a/packages/calculators/src/modules/test/4.7-other-livestock-manure/4.7-other-livestock-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.7-other-livestock-manure/4.7-other-livestock-manure.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/4.7-other-livestock-manure/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD764D7-C81C-164A-910C-77EE6504A08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA9EEBE-9F0E-814B-8B85-194AAC47673F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15880" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="4.7.1.1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -574,6 +572,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1023,8 +1046,8 @@
         <v>36</v>
       </c>
       <c r="AN4">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="AP4" t="s">
         <v>48</v>
@@ -1316,7 +1339,7 @@
       </c>
       <c r="O11">
         <f t="shared" ref="O11:O29" si="0">$AN$4</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P11">
         <f>VLOOKUP(A11, $AM$11:$AO$18,3,FALSE)</f>
@@ -1384,7 +1407,7 @@
       </c>
       <c r="AF11">
         <f>AE11*W11*O11*10^-3</f>
-        <v>0.6796821428571429</v>
+        <v>0.67906425000000015</v>
       </c>
       <c r="AG11">
         <f>AE11*S11</f>
@@ -1392,7 +1415,7 @@
       </c>
       <c r="AH11">
         <f>AG11*Q11*O11*10^-3</f>
-        <v>0.16652212499999999</v>
+        <v>0.16637074125000001</v>
       </c>
       <c r="AI11">
         <f>AE11*R11*T11</f>
@@ -1400,7 +1423,7 @@
       </c>
       <c r="AJ11">
         <f>AI11*U11*O11*10^-3</f>
-        <v>0.29906014285714283</v>
+        <v>0.29878826999999997</v>
       </c>
       <c r="AM11" s="2" t="s">
         <v>3</v>
@@ -1467,7 +1490,7 @@
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P12">
         <f>VLOOKUP(A12, $AM$11:$AO$18,3,FALSE)</f>
@@ -1535,7 +1558,7 @@
       </c>
       <c r="AF12">
         <f t="shared" ref="AF12:AF17" si="10">AE12*W12*O12*10^-3</f>
-        <v>0.81561857142857142</v>
+        <v>0.81487710000000002</v>
       </c>
       <c r="AG12">
         <f t="shared" ref="AG12:AG17" si="11">AE12*S12</f>
@@ -1543,7 +1566,7 @@
       </c>
       <c r="AH12">
         <f t="shared" ref="AH12:AH17" si="12">AG12*Q12*O12*10^-3</f>
-        <v>0.19982654999999999</v>
+        <v>0.19964488950000001</v>
       </c>
       <c r="AI12">
         <f t="shared" ref="AI12:AI17" si="13">AE12*R12*T12</f>
@@ -1618,7 +1641,7 @@
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P13">
         <f t="shared" ref="P13:P17" si="18">VLOOKUP(A13, $AM$11:$AO$18,3,FALSE)</f>
@@ -1686,7 +1709,7 @@
       </c>
       <c r="AF13">
         <f t="shared" si="10"/>
-        <v>0.95155499999999993</v>
+        <v>0.95068995000000001</v>
       </c>
       <c r="AG13">
         <f t="shared" si="11"/>
@@ -1694,7 +1717,7 @@
       </c>
       <c r="AH13">
         <f t="shared" si="12"/>
-        <v>0.19649610749999999</v>
+        <v>0.19631747467499999</v>
       </c>
       <c r="AI13">
         <f t="shared" si="13"/>
@@ -1702,7 +1725,7 @@
       </c>
       <c r="AJ13">
         <f t="shared" si="14"/>
-        <v>0.41868419999999995</v>
+        <v>0.41830357799999995</v>
       </c>
       <c r="AM13" s="2" t="s">
         <v>22</v>
@@ -1769,7 +1792,7 @@
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P14">
         <f t="shared" si="18"/>
@@ -1837,7 +1860,7 @@
       </c>
       <c r="AF14">
         <f t="shared" si="10"/>
-        <v>1.0874914285714286</v>
+        <v>1.0865028000000001</v>
       </c>
       <c r="AG14">
         <f t="shared" si="11"/>
@@ -1845,7 +1868,7 @@
       </c>
       <c r="AH14">
         <f t="shared" si="12"/>
-        <v>0.26643539999999999</v>
+        <v>0.26619318599999997</v>
       </c>
       <c r="AI14">
         <f t="shared" si="13"/>
@@ -1920,7 +1943,7 @@
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P15">
         <f t="shared" si="18"/>
@@ -1988,7 +2011,7 @@
       </c>
       <c r="AF15">
         <f t="shared" si="10"/>
-        <v>0.21681</v>
+        <v>0.2166129</v>
       </c>
       <c r="AG15">
         <f t="shared" si="11"/>
@@ -1996,7 +2019,7 @@
       </c>
       <c r="AH15">
         <f t="shared" si="12"/>
-        <v>1.3659029999999999E-2</v>
+        <v>1.3646612700000001E-2</v>
       </c>
       <c r="AI15">
         <f t="shared" si="13"/>
@@ -2004,7 +2027,7 @@
       </c>
       <c r="AJ15">
         <f t="shared" si="14"/>
-        <v>9.5396400000000006E-2</v>
+        <v>9.530967600000001E-2</v>
       </c>
       <c r="AM15" s="2" t="s">
         <v>18</v>
@@ -2071,7 +2094,7 @@
       </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P16">
         <f t="shared" si="18"/>
@@ -2139,7 +2162,7 @@
       </c>
       <c r="AF16">
         <f t="shared" si="10"/>
-        <v>0.2409</v>
+        <v>0.24068100000000003</v>
       </c>
       <c r="AG16">
         <f t="shared" si="11"/>
@@ -2147,7 +2170,7 @@
       </c>
       <c r="AH16">
         <f t="shared" si="12"/>
-        <v>2.4451349999999997E-2</v>
+        <v>2.4429121500000001E-2</v>
       </c>
       <c r="AI16">
         <f t="shared" si="13"/>
@@ -2222,7 +2245,7 @@
       </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P17">
         <f t="shared" si="18"/>
@@ -2290,7 +2313,7 @@
       </c>
       <c r="AF17">
         <f t="shared" si="10"/>
-        <v>8.8330000000000006E-2</v>
+        <v>8.82497E-2</v>
       </c>
       <c r="AG17">
         <f t="shared" si="11"/>
@@ -2298,7 +2321,7 @@
       </c>
       <c r="AH17">
         <f t="shared" si="12"/>
-        <v>7.4197199999999991E-2</v>
+        <v>7.4129748000000009E-2</v>
       </c>
       <c r="AI17">
         <f t="shared" si="13"/>
@@ -2306,7 +2329,7 @@
       </c>
       <c r="AJ17">
         <f t="shared" si="14"/>
-        <v>0.11659559999999999</v>
+        <v>0.116489604</v>
       </c>
       <c r="AM17" s="2" t="s">
         <v>20</v>
@@ -2373,7 +2396,7 @@
       </c>
       <c r="O18">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18:P29" si="30">VLOOKUP(A18, $AM$11:$AO$18,3,FALSE)</f>
@@ -2441,7 +2464,7 @@
       </c>
       <c r="AF18">
         <f t="shared" ref="AF18:AF29" si="41">AE18*W18*O18*10^-3</f>
-        <v>0.10439000000000001</v>
+        <v>0.10429510000000002</v>
       </c>
       <c r="AG18">
         <f t="shared" ref="AG18:AG29" si="42">AE18*S18</f>
@@ -2449,7 +2472,7 @@
       </c>
       <c r="AH18">
         <f t="shared" ref="AH18:AH29" si="43">AG18*Q18*O18*10^-3</f>
-        <v>7.6726649999999993E-2</v>
+        <v>7.6656898500000001E-2</v>
       </c>
       <c r="AI18">
         <f t="shared" ref="AI18:AI29" si="44">AE18*R18*T18</f>
@@ -2457,7 +2480,7 @@
       </c>
       <c r="AJ18">
         <f t="shared" ref="AJ18:AJ29" si="45">AI18*U18*O18*10^-3</f>
-        <v>0.1377948</v>
+        <v>0.13766953199999998</v>
       </c>
       <c r="AM18" s="2" t="s">
         <v>62</v>
@@ -2524,7 +2547,7 @@
       </c>
       <c r="O19">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P19">
         <f t="shared" si="30"/>
@@ -2592,7 +2615,7 @@
       </c>
       <c r="AF19">
         <f t="shared" si="41"/>
-        <v>0.11242000000000001</v>
+        <v>0.11231780000000002</v>
       </c>
       <c r="AG19">
         <f t="shared" si="42"/>
@@ -2600,7 +2623,7 @@
       </c>
       <c r="AH19">
         <f t="shared" si="43"/>
-        <v>2.1247379999999996E-2</v>
+        <v>2.1228064200000001E-2</v>
       </c>
       <c r="AI19">
         <f t="shared" si="44"/>
@@ -2666,7 +2689,7 @@
       </c>
       <c r="O20">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P20">
         <f t="shared" si="30"/>
@@ -2734,7 +2757,7 @@
       </c>
       <c r="AF20">
         <f t="shared" si="41"/>
-        <v>0.36135</v>
+        <v>0.36102150000000005</v>
       </c>
       <c r="AG20">
         <f t="shared" si="42"/>
@@ -2742,7 +2765,7 @@
       </c>
       <c r="AH20">
         <f t="shared" si="43"/>
-        <v>3.6677024999999995E-2</v>
+        <v>3.6643682249999997E-2</v>
       </c>
       <c r="AI20">
         <f t="shared" si="44"/>
@@ -2750,7 +2773,7 @@
       </c>
       <c r="AJ20">
         <f t="shared" si="45"/>
-        <v>0.158994</v>
+        <v>0.15884946</v>
       </c>
       <c r="AP20" s="2"/>
       <c r="AQ20" s="2"/>
@@ -2808,7 +2831,7 @@
       </c>
       <c r="O21">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P21">
         <f t="shared" si="30"/>
@@ -2876,7 +2899,7 @@
       </c>
       <c r="AF21">
         <f t="shared" si="41"/>
-        <v>0.7268297142857143</v>
+        <v>0.72616896000000009</v>
       </c>
       <c r="AG21">
         <f t="shared" si="42"/>
@@ -2884,7 +2907,7 @@
       </c>
       <c r="AH21">
         <f t="shared" si="43"/>
-        <v>0.20351232</v>
+        <v>0.2033273088</v>
       </c>
       <c r="AI21">
         <f t="shared" si="44"/>
@@ -2956,7 +2979,7 @@
       </c>
       <c r="O22">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P22">
         <f t="shared" si="30"/>
@@ -3024,7 +3047,7 @@
       </c>
       <c r="AF22">
         <f t="shared" si="41"/>
-        <v>0.77225657142857129</v>
+        <v>0.77155451999999991</v>
       </c>
       <c r="AG22">
         <f t="shared" si="42"/>
@@ -3032,7 +3055,7 @@
       </c>
       <c r="AH22">
         <f t="shared" si="43"/>
-        <v>0.15947098199999993</v>
+        <v>0.15932600837999997</v>
       </c>
       <c r="AI22">
         <f t="shared" si="44"/>
@@ -3040,7 +3063,7 @@
       </c>
       <c r="AJ22">
         <f t="shared" si="45"/>
-        <v>0.33979289142857128</v>
+        <v>0.33948398879999991</v>
       </c>
       <c r="AM22" s="2" t="s">
         <v>25</v>
@@ -3099,7 +3122,7 @@
       </c>
       <c r="O23">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P23">
         <f t="shared" si="30"/>
@@ -3167,7 +3190,7 @@
       </c>
       <c r="AF23">
         <f t="shared" si="41"/>
-        <v>0.81768342857142862</v>
+        <v>0.81694008000000007</v>
       </c>
       <c r="AG23">
         <f t="shared" si="42"/>
@@ -3175,7 +3198,7 @@
       </c>
       <c r="AH23">
         <f t="shared" si="43"/>
-        <v>0.20033244000000003</v>
+        <v>0.20015031960000002</v>
       </c>
       <c r="AI23">
         <f t="shared" si="44"/>
@@ -3240,7 +3263,7 @@
       </c>
       <c r="O24">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P24">
         <f t="shared" si="30"/>
@@ -3308,7 +3331,7 @@
       </c>
       <c r="AF24">
         <f t="shared" si="41"/>
-        <v>0.86311028571428583</v>
+        <v>0.86232564000000012</v>
       </c>
       <c r="AG24">
         <f t="shared" si="42"/>
@@ -3316,7 +3339,7 @@
       </c>
       <c r="AH24">
         <f t="shared" si="43"/>
-        <v>5.4375948E-2</v>
+        <v>5.4326515320000004E-2</v>
       </c>
       <c r="AI24">
         <f t="shared" si="44"/>
@@ -3324,7 +3347,7 @@
       </c>
       <c r="AJ24">
         <f t="shared" si="45"/>
-        <v>0.37976852571428565</v>
+        <v>0.37942328159999994</v>
       </c>
       <c r="AM24" s="2" t="s">
         <v>63</v>
@@ -3382,7 +3405,7 @@
       </c>
       <c r="O25">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P25">
         <f t="shared" si="30"/>
@@ -3450,7 +3473,7 @@
       </c>
       <c r="AF25">
         <f t="shared" si="41"/>
-        <v>2.7187285714285716</v>
+        <v>2.7162570000000006</v>
       </c>
       <c r="AG25">
         <f t="shared" si="42"/>
@@ -3458,7 +3481,7 @@
       </c>
       <c r="AH25">
         <f t="shared" si="43"/>
-        <v>0.27595094999999997</v>
+        <v>0.27570008550000003</v>
       </c>
       <c r="AI25">
         <f t="shared" si="44"/>
@@ -3524,7 +3547,7 @@
       </c>
       <c r="O26">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P26">
         <f t="shared" si="30"/>
@@ -3592,7 +3615,7 @@
       </c>
       <c r="AF26">
         <f t="shared" si="41"/>
-        <v>0.16863</v>
+        <v>0.16847670000000003</v>
       </c>
       <c r="AG26">
         <f t="shared" si="42"/>
@@ -3600,7 +3623,7 @@
       </c>
       <c r="AH26">
         <f t="shared" si="43"/>
-        <v>0.1416492</v>
+        <v>0.141520428</v>
       </c>
       <c r="AI26">
         <f t="shared" si="44"/>
@@ -3608,7 +3631,7 @@
       </c>
       <c r="AJ26">
         <f t="shared" si="45"/>
-        <v>0.22259159999999997</v>
+        <v>0.22238924399999996</v>
       </c>
       <c r="AM26" s="2" t="s">
         <v>65</v>
@@ -3666,7 +3689,7 @@
       </c>
       <c r="O27">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P27">
         <f t="shared" si="30"/>
@@ -3734,7 +3757,7 @@
       </c>
       <c r="AF27">
         <f t="shared" si="41"/>
-        <v>0.99686714285714295</v>
+        <v>0.99596090000000004</v>
       </c>
       <c r="AG27">
         <f t="shared" si="42"/>
@@ -3742,7 +3765,7 @@
       </c>
       <c r="AH27">
         <f t="shared" si="43"/>
-        <v>0.61755919499999989</v>
+        <v>0.61699777754999996</v>
       </c>
       <c r="AI27">
         <f t="shared" si="44"/>
@@ -3808,7 +3831,7 @@
       </c>
       <c r="O28">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P28">
         <f t="shared" si="30"/>
@@ -3876,7 +3899,7 @@
       </c>
       <c r="AF28">
         <f t="shared" si="41"/>
-        <v>0.34827257142857138</v>
+        <v>0.34795596000000001</v>
       </c>
       <c r="AG28">
         <f t="shared" si="42"/>
@@ -3884,7 +3907,7 @@
       </c>
       <c r="AH28">
         <f t="shared" si="43"/>
-        <v>0.25598033999999997</v>
+        <v>0.2557476306</v>
       </c>
       <c r="AI28">
         <f t="shared" si="44"/>
@@ -3892,7 +3915,7 @@
       </c>
       <c r="AJ28">
         <f t="shared" si="45"/>
-        <v>0.45971979428571424</v>
+        <v>0.45930186719999994</v>
       </c>
       <c r="AM28" s="2" t="s">
         <v>67</v>
@@ -3950,7 +3973,7 @@
       </c>
       <c r="O29">
         <f t="shared" si="0"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P29">
         <f t="shared" si="30"/>
@@ -4018,7 +4041,7 @@
       </c>
       <c r="AF29">
         <f t="shared" si="41"/>
-        <v>0.19272</v>
+        <v>0.19254480000000002</v>
       </c>
       <c r="AG29">
         <f t="shared" si="42"/>
@@ -4026,7 +4049,7 @@
       </c>
       <c r="AH29">
         <f t="shared" si="43"/>
-        <v>3.6424079999999998E-2</v>
+        <v>3.6390967199999999E-2</v>
       </c>
       <c r="AI29">
         <f t="shared" si="44"/>
@@ -4223,7 +4246,7 @@
       </c>
       <c r="O41">
         <f t="shared" ref="O41:O59" si="47">$AN$4</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P41">
         <f>VLOOKUP(A41, $AM$11:$AO$18,3,FALSE)</f>
@@ -4327,7 +4350,7 @@
       </c>
       <c r="O42">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P42">
         <f>VLOOKUP(A42, $AM$11:$AO$18,3,FALSE)</f>
@@ -4431,7 +4454,7 @@
       </c>
       <c r="O43">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P43">
         <f t="shared" ref="P43:P47" si="56">VLOOKUP(A43, $AM$11:$AO$18,3,FALSE)</f>
@@ -4535,7 +4558,7 @@
       </c>
       <c r="O44">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P44">
         <f t="shared" si="56"/>
@@ -4639,7 +4662,7 @@
       </c>
       <c r="O45">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P45">
         <f t="shared" si="56"/>
@@ -4743,7 +4766,7 @@
       </c>
       <c r="O46">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P46">
         <f t="shared" si="56"/>
@@ -4847,7 +4870,7 @@
       </c>
       <c r="O47">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P47">
         <f t="shared" si="56"/>
@@ -4951,7 +4974,7 @@
       </c>
       <c r="O48">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P48">
         <f t="shared" ref="P48:P59" si="66">VLOOKUP(A48, $AM$11:$AO$18,3,FALSE)</f>
@@ -5055,7 +5078,7 @@
       </c>
       <c r="O49">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P49">
         <f t="shared" si="66"/>
@@ -5159,7 +5182,7 @@
       </c>
       <c r="O50">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P50">
         <f t="shared" si="66"/>
@@ -5263,7 +5286,7 @@
       </c>
       <c r="O51">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P51">
         <f t="shared" si="66"/>
@@ -5367,7 +5390,7 @@
       </c>
       <c r="O52">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P52">
         <f t="shared" si="66"/>
@@ -5471,7 +5494,7 @@
       </c>
       <c r="O53">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P53">
         <f t="shared" si="66"/>
@@ -5575,7 +5598,7 @@
       </c>
       <c r="O54">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P54">
         <f t="shared" si="66"/>
@@ -5679,7 +5702,7 @@
       </c>
       <c r="O55">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P55">
         <f t="shared" si="66"/>
@@ -5783,7 +5806,7 @@
       </c>
       <c r="O56">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P56">
         <f t="shared" si="66"/>
@@ -5881,7 +5904,7 @@
       </c>
       <c r="O57">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P57">
         <f t="shared" si="66"/>
@@ -5979,7 +6002,7 @@
       </c>
       <c r="O58">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P58">
         <f t="shared" si="66"/>
@@ -6077,7 +6100,7 @@
       </c>
       <c r="O59">
         <f t="shared" si="47"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="P59">
         <f t="shared" si="66"/>

--- a/packages/calculators/src/modules/test/4.7-other-livestock-manure/4.7-other-livestock-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.7-other-livestock-manure/4.7-other-livestock-manure.xlsx
@@ -1402,28 +1402,28 @@
         <v>3.0183028512000003E-3</v>
       </c>
       <c r="AE11">
-        <f>C11*P11*365</f>
-        <v>72087.5</v>
+        <f>C11*P11</f>
+        <v>197.5</v>
       </c>
       <c r="AF11">
         <f>AE11*W11*O11*10^-3</f>
-        <v>0.67906425000000015</v>
+        <v>0.0018604500000000003</v>
       </c>
       <c r="AG11">
         <f>AE11*S11</f>
-        <v>15138.375</v>
+        <v>41.475</v>
       </c>
       <c r="AH11">
         <f>AG11*Q11*O11*10^-3</f>
-        <v>0.16637074125000001</v>
+        <v>0.00045581025000000005</v>
       </c>
       <c r="AI11">
         <f>AE11*R11*T11</f>
-        <v>17301</v>
+        <v>47.4</v>
       </c>
       <c r="AJ11">
         <f>AI11*U11*O11*10^-3</f>
-        <v>0.29878826999999997</v>
+        <v>0.000818598</v>
       </c>
       <c r="AM11" s="2" t="s">
         <v>3</v>
@@ -1553,20 +1553,20 @@
         <v>3.6219634214400007E-3</v>
       </c>
       <c r="AE12">
-        <f t="shared" ref="AE12:AE17" si="9">C12*P12*365</f>
-        <v>86505</v>
+        <f t="shared" ref="AE12:AE17" si="9">C12*P12</f>
+        <v>237</v>
       </c>
       <c r="AF12">
         <f t="shared" ref="AF12:AF17" si="10">AE12*W12*O12*10^-3</f>
-        <v>0.81487710000000002</v>
+        <v>0.0022325400000000003</v>
       </c>
       <c r="AG12">
         <f t="shared" ref="AG12:AG17" si="11">AE12*S12</f>
-        <v>18166.05</v>
+        <v>49.769999999999996</v>
       </c>
       <c r="AH12">
         <f t="shared" ref="AH12:AH17" si="12">AG12*Q12*O12*10^-3</f>
-        <v>0.19964488950000001</v>
+        <v>0.0005469723</v>
       </c>
       <c r="AI12">
         <f t="shared" ref="AI12:AI17" si="13">AE12*R12*T12</f>
@@ -1705,27 +1705,27 @@
       </c>
       <c r="AE13">
         <f t="shared" si="9"/>
-        <v>100922.5</v>
+        <v>276.5</v>
       </c>
       <c r="AF13">
         <f t="shared" si="10"/>
-        <v>0.95068995000000001</v>
+        <v>0.00260463</v>
       </c>
       <c r="AG13">
         <f t="shared" si="11"/>
-        <v>21193.724999999999</v>
+        <v>58.065</v>
       </c>
       <c r="AH13">
         <f t="shared" si="12"/>
-        <v>0.19631747467499999</v>
+        <v>0.000537856095</v>
       </c>
       <c r="AI13">
         <f t="shared" si="13"/>
-        <v>24221.399999999998</v>
+        <v>66.36</v>
       </c>
       <c r="AJ13">
         <f t="shared" si="14"/>
-        <v>0.41830357799999995</v>
+        <v>0.0011460372</v>
       </c>
       <c r="AM13" s="2" t="s">
         <v>22</v>
@@ -1856,19 +1856,19 @@
       </c>
       <c r="AE14">
         <f t="shared" si="9"/>
-        <v>115340</v>
+        <v>316</v>
       </c>
       <c r="AF14">
         <f t="shared" si="10"/>
-        <v>1.0865028000000001</v>
+        <v>0.0029767200000000004</v>
       </c>
       <c r="AG14">
         <f t="shared" si="11"/>
-        <v>24221.399999999998</v>
+        <v>66.36</v>
       </c>
       <c r="AH14">
         <f t="shared" si="12"/>
-        <v>0.26619318599999997</v>
+        <v>0.0007292964</v>
       </c>
       <c r="AI14">
         <f t="shared" si="13"/>
@@ -2007,27 +2007,27 @@
       </c>
       <c r="AE15">
         <f t="shared" si="9"/>
-        <v>22995</v>
+        <v>63</v>
       </c>
       <c r="AF15">
         <f t="shared" si="10"/>
-        <v>0.2166129</v>
+        <v>0.00059346</v>
       </c>
       <c r="AG15">
         <f t="shared" si="11"/>
-        <v>4828.95</v>
+        <v>13.229999999999999</v>
       </c>
       <c r="AH15">
         <f t="shared" si="12"/>
-        <v>1.3646612700000001E-2</v>
+        <v>0.00003738798</v>
       </c>
       <c r="AI15">
         <f t="shared" si="13"/>
-        <v>5518.8</v>
+        <v>15.12</v>
       </c>
       <c r="AJ15">
         <f t="shared" si="14"/>
-        <v>9.530967600000001E-2</v>
+        <v>0.0002611224</v>
       </c>
       <c r="AM15" s="2" t="s">
         <v>18</v>
@@ -2158,19 +2158,19 @@
       </c>
       <c r="AE16">
         <f t="shared" si="9"/>
-        <v>25550</v>
+        <v>70</v>
       </c>
       <c r="AF16">
         <f t="shared" si="10"/>
-        <v>0.24068100000000003</v>
+        <v>0.0006594</v>
       </c>
       <c r="AG16">
         <f t="shared" si="11"/>
-        <v>5365.5</v>
+        <v>14.7</v>
       </c>
       <c r="AH16">
         <f t="shared" si="12"/>
-        <v>2.4429121500000001E-2</v>
+        <v>0.00006692909999999999</v>
       </c>
       <c r="AI16">
         <f t="shared" si="13"/>
@@ -2309,27 +2309,27 @@
       </c>
       <c r="AE17">
         <f t="shared" si="9"/>
-        <v>28105</v>
+        <v>77</v>
       </c>
       <c r="AF17">
         <f t="shared" si="10"/>
-        <v>8.82497E-2</v>
+        <v>0.00024178</v>
       </c>
       <c r="AG17">
         <f t="shared" si="11"/>
-        <v>5902.05</v>
+        <v>16.169999999999998</v>
       </c>
       <c r="AH17">
         <f t="shared" si="12"/>
-        <v>7.4129748000000009E-2</v>
+        <v>0.0002030952</v>
       </c>
       <c r="AI17">
         <f t="shared" si="13"/>
-        <v>6745.2</v>
+        <v>18.48</v>
       </c>
       <c r="AJ17">
         <f t="shared" si="14"/>
-        <v>0.116489604</v>
+        <v>0.0003191496</v>
       </c>
       <c r="AM17" s="2" t="s">
         <v>20</v>
@@ -2459,28 +2459,28 @@
         <v>9.7735520896000019E-4</v>
       </c>
       <c r="AE18">
-        <f t="shared" ref="AE18:AE29" si="40">C18*P18*365</f>
-        <v>33215</v>
+        <f t="shared" ref="AE18:AE29" si="40">C18*P18</f>
+        <v>91</v>
       </c>
       <c r="AF18">
         <f t="shared" ref="AF18:AF29" si="41">AE18*W18*O18*10^-3</f>
-        <v>0.10429510000000002</v>
+        <v>0.00028574</v>
       </c>
       <c r="AG18">
         <f t="shared" ref="AG18:AG29" si="42">AE18*S18</f>
-        <v>6975.15</v>
+        <v>19.11</v>
       </c>
       <c r="AH18">
         <f t="shared" ref="AH18:AH29" si="43">AG18*Q18*O18*10^-3</f>
-        <v>7.6656898500000001E-2</v>
+        <v>0.0002100189</v>
       </c>
       <c r="AI18">
         <f t="shared" ref="AI18:AI29" si="44">AE18*R18*T18</f>
-        <v>7971.5999999999995</v>
+        <v>21.84</v>
       </c>
       <c r="AJ18">
         <f t="shared" ref="AJ18:AJ29" si="45">AI18*U18*O18*10^-3</f>
-        <v>0.13766953199999998</v>
+        <v>0.0003771768</v>
       </c>
       <c r="AM18" s="2" t="s">
         <v>62</v>
@@ -2611,19 +2611,19 @@
       </c>
       <c r="AE19">
         <f t="shared" si="40"/>
-        <v>35770</v>
+        <v>98</v>
       </c>
       <c r="AF19">
         <f t="shared" si="41"/>
-        <v>0.11231780000000002</v>
+        <v>0.00030772000000000004</v>
       </c>
       <c r="AG19">
         <f t="shared" si="42"/>
-        <v>7511.7</v>
+        <v>20.58</v>
       </c>
       <c r="AH19">
         <f t="shared" si="43"/>
-        <v>2.1228064200000001E-2</v>
+        <v>0.000058159079999999995</v>
       </c>
       <c r="AI19">
         <f t="shared" si="44"/>
@@ -2753,27 +2753,27 @@
       </c>
       <c r="AE20">
         <f t="shared" si="40"/>
-        <v>38325</v>
+        <v>105</v>
       </c>
       <c r="AF20">
         <f t="shared" si="41"/>
-        <v>0.36102150000000005</v>
+        <v>0.0009891000000000001</v>
       </c>
       <c r="AG20">
         <f t="shared" si="42"/>
-        <v>8048.25</v>
+        <v>22.05</v>
       </c>
       <c r="AH20">
         <f t="shared" si="43"/>
-        <v>3.6643682249999997E-2</v>
+        <v>0.00010039365</v>
       </c>
       <c r="AI20">
         <f t="shared" si="44"/>
-        <v>9198</v>
+        <v>25.2</v>
       </c>
       <c r="AJ20">
         <f t="shared" si="45"/>
-        <v>0.15884946</v>
+        <v>0.00043520400000000007</v>
       </c>
       <c r="AP20" s="2"/>
       <c r="AQ20" s="2"/>
@@ -2895,19 +2895,19 @@
       </c>
       <c r="AE21">
         <f t="shared" si="40"/>
-        <v>77088</v>
+        <v>211.2</v>
       </c>
       <c r="AF21">
         <f t="shared" si="41"/>
-        <v>0.72616896000000009</v>
+        <v>0.001989504</v>
       </c>
       <c r="AG21">
         <f t="shared" si="42"/>
-        <v>16188.48</v>
+        <v>44.352</v>
       </c>
       <c r="AH21">
         <f t="shared" si="43"/>
-        <v>0.2033273088</v>
+        <v>0.0005570611199999999</v>
       </c>
       <c r="AI21">
         <f t="shared" si="44"/>
@@ -3043,27 +3043,27 @@
       </c>
       <c r="AE22">
         <f t="shared" si="40"/>
-        <v>81905.999999999985</v>
+        <v>224.39999999999998</v>
       </c>
       <c r="AF22">
         <f t="shared" si="41"/>
-        <v>0.77155451999999991</v>
+        <v>0.002113848</v>
       </c>
       <c r="AG22">
         <f t="shared" si="42"/>
-        <v>17200.259999999995</v>
+        <v>47.123999999999995</v>
       </c>
       <c r="AH22">
         <f t="shared" si="43"/>
-        <v>0.15932600837999997</v>
+        <v>0.000436509612</v>
       </c>
       <c r="AI22">
         <f t="shared" si="44"/>
-        <v>19657.439999999995</v>
+        <v>53.855999999999995</v>
       </c>
       <c r="AJ22">
         <f t="shared" si="45"/>
-        <v>0.33948398879999991</v>
+        <v>0.0009300931200000001</v>
       </c>
       <c r="AM22" s="2" t="s">
         <v>25</v>
@@ -3186,19 +3186,19 @@
       </c>
       <c r="AE23">
         <f t="shared" si="40"/>
-        <v>86724</v>
+        <v>237.6</v>
       </c>
       <c r="AF23">
         <f t="shared" si="41"/>
-        <v>0.81694008000000007</v>
+        <v>0.0022381920000000004</v>
       </c>
       <c r="AG23">
         <f t="shared" si="42"/>
-        <v>18212.04</v>
+        <v>49.895999999999994</v>
       </c>
       <c r="AH23">
         <f t="shared" si="43"/>
-        <v>0.20015031960000002</v>
+        <v>0.00054835704</v>
       </c>
       <c r="AI23">
         <f t="shared" si="44"/>
@@ -3327,27 +3327,27 @@
       </c>
       <c r="AE24">
         <f t="shared" si="40"/>
-        <v>91542</v>
+        <v>250.79999999999998</v>
       </c>
       <c r="AF24">
         <f t="shared" si="41"/>
-        <v>0.86232564000000012</v>
+        <v>0.002362536</v>
       </c>
       <c r="AG24">
         <f t="shared" si="42"/>
-        <v>19223.82</v>
+        <v>52.66799999999999</v>
       </c>
       <c r="AH24">
         <f t="shared" si="43"/>
-        <v>5.4326515320000004E-2</v>
+        <v>0.000148839768</v>
       </c>
       <c r="AI24">
         <f t="shared" si="44"/>
-        <v>21970.079999999998</v>
+        <v>60.19199999999999</v>
       </c>
       <c r="AJ24">
         <f t="shared" si="45"/>
-        <v>0.37942328159999994</v>
+        <v>0.00103951584</v>
       </c>
       <c r="AM24" s="2" t="s">
         <v>63</v>
@@ -3469,19 +3469,19 @@
       </c>
       <c r="AE25">
         <f t="shared" si="40"/>
-        <v>288350</v>
+        <v>790</v>
       </c>
       <c r="AF25">
         <f t="shared" si="41"/>
-        <v>2.7162570000000006</v>
+        <v>0.007441800000000001</v>
       </c>
       <c r="AG25">
         <f t="shared" si="42"/>
-        <v>60553.5</v>
+        <v>165.9</v>
       </c>
       <c r="AH25">
         <f t="shared" si="43"/>
-        <v>0.27570008550000003</v>
+        <v>0.0007553427</v>
       </c>
       <c r="AI25">
         <f t="shared" si="44"/>
@@ -3611,27 +3611,27 @@
       </c>
       <c r="AE26">
         <f t="shared" si="40"/>
-        <v>53655</v>
+        <v>147</v>
       </c>
       <c r="AF26">
         <f t="shared" si="41"/>
-        <v>0.16847670000000003</v>
+        <v>0.00046158</v>
       </c>
       <c r="AG26">
         <f t="shared" si="42"/>
-        <v>11267.55</v>
+        <v>30.869999999999997</v>
       </c>
       <c r="AH26">
         <f t="shared" si="43"/>
-        <v>0.141520428</v>
+        <v>0.0003877272</v>
       </c>
       <c r="AI26">
         <f t="shared" si="44"/>
-        <v>12877.199999999999</v>
+        <v>35.28</v>
       </c>
       <c r="AJ26">
         <f t="shared" si="45"/>
-        <v>0.22238924399999996</v>
+        <v>0.0006092856</v>
       </c>
       <c r="AM26" s="2" t="s">
         <v>65</v>
@@ -3753,19 +3753,19 @@
       </c>
       <c r="AE27">
         <f t="shared" si="40"/>
-        <v>317185</v>
+        <v>869</v>
       </c>
       <c r="AF27">
         <f t="shared" si="41"/>
-        <v>0.99596090000000004</v>
+        <v>0.00272866</v>
       </c>
       <c r="AG27">
         <f t="shared" si="42"/>
-        <v>66608.849999999991</v>
+        <v>182.48999999999998</v>
       </c>
       <c r="AH27">
         <f t="shared" si="43"/>
-        <v>0.61699777754999996</v>
+        <v>0.00169040487</v>
       </c>
       <c r="AI27">
         <f t="shared" si="44"/>
@@ -3895,27 +3895,27 @@
       </c>
       <c r="AE28">
         <f t="shared" si="40"/>
-        <v>110813.99999999999</v>
+        <v>303.59999999999997</v>
       </c>
       <c r="AF28">
         <f t="shared" si="41"/>
-        <v>0.34795596000000001</v>
+        <v>0.000953304</v>
       </c>
       <c r="AG28">
         <f t="shared" si="42"/>
-        <v>23270.939999999995</v>
+        <v>63.75599999999999</v>
       </c>
       <c r="AH28">
         <f t="shared" si="43"/>
-        <v>0.2557476306</v>
+        <v>0.00070067844</v>
       </c>
       <c r="AI28">
         <f t="shared" si="44"/>
-        <v>26595.359999999997</v>
+        <v>72.86399999999999</v>
       </c>
       <c r="AJ28">
         <f t="shared" si="45"/>
-        <v>0.45930186719999994</v>
+        <v>0.00125836128</v>
       </c>
       <c r="AM28" s="2" t="s">
         <v>67</v>
@@ -4037,19 +4037,19 @@
       </c>
       <c r="AE29">
         <f t="shared" si="40"/>
-        <v>61320</v>
+        <v>168</v>
       </c>
       <c r="AF29">
         <f t="shared" si="41"/>
-        <v>0.19254480000000002</v>
+        <v>0.0005275200000000001</v>
       </c>
       <c r="AG29">
         <f t="shared" si="42"/>
-        <v>12877.199999999999</v>
+        <v>35.28</v>
       </c>
       <c r="AH29">
         <f t="shared" si="43"/>
-        <v>3.6390967199999999E-2</v>
+        <v>0.00009970128000000002</v>
       </c>
       <c r="AI29">
         <f t="shared" si="44"/>
